--- a/600.store/model.orm.xlsx
+++ b/600.store/model.orm.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="12555" activeTab="3"/>
+    <workbookView windowWidth="28800" windowHeight="12555" activeTab="4"/>
   </bookViews>
   <sheets>
     <sheet name="配置" sheetId="2" r:id="rId1"/>
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="305" uniqueCount="150">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="317" uniqueCount="155">
   <si>
     <t>#变量名</t>
   </si>
@@ -140,7 +140,7 @@
     <t>createTime</t>
   </si>
   <si>
-    <t>TIMESTAMP</t>
+    <t>BIGINT</t>
   </si>
   <si>
     <t>updateTime</t>
@@ -158,7 +158,7 @@
     <t>boolFlag</t>
   </si>
   <si>
-    <t>TINYINT</t>
+    <t>BOOLEAN</t>
   </si>
   <si>
     <t>image</t>
@@ -350,9 +350,6 @@
     <t>出生日期</t>
   </si>
   <si>
-    <t>BIGINT</t>
-  </si>
-  <si>
     <t>毫秒值，避免处理时区</t>
   </si>
   <si>
@@ -368,12 +365,18 @@
     <t>「我」？</t>
   </si>
   <si>
-    <t>BOOLEAN</t>
-  </si>
-  <si>
     <t>是否为资产库所有者。有且仅有一个</t>
   </si>
   <si>
+    <t>deleted</t>
+  </si>
+  <si>
+    <t>是否已删除</t>
+  </si>
+  <si>
+    <t>软删除标记</t>
+  </si>
+  <si>
     <t>唯一键列表</t>
   </si>
   <si>
@@ -425,7 +428,7 @@
     <t>o_person_relationship</t>
   </si>
   <si>
-    <t>PersonRelationShip</t>
+    <t>PersonRelationship</t>
   </si>
   <si>
     <t>个体间的（直接）关系</t>
@@ -452,19 +455,31 @@
     <t>关系类型</t>
   </si>
   <si>
+    <t>UK_o_person_relationship_sourceId_targetId</t>
+  </si>
+  <si>
+    <t>sourceId,targetId</t>
+  </si>
+  <si>
     <t>source</t>
   </si>
   <si>
+    <t>relationToList</t>
+  </si>
+  <si>
     <t>to-one</t>
   </si>
   <si>
-    <t>cascade-delete</t>
+    <t>pub,ref-pub,ref-cascade-delete</t>
   </si>
   <si>
     <t>sourceId</t>
   </si>
   <si>
     <t>target</t>
+  </si>
+  <si>
+    <t>relationFromList</t>
   </si>
   <si>
     <t>targetId</t>
@@ -1368,7 +1383,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="76">
+  <cellXfs count="77">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1426,6 +1441,9 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1451,59 +1469,68 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="14" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="14" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="14" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1561,9 +1588,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="49" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="10" borderId="3" xfId="49" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1575,12 +1599,6 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="49" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="14" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1927,144 +1945,144 @@
   </cols>
   <sheetData>
     <row r="1" s="2" customFormat="1" spans="1:3">
-      <c r="A1" s="73" t="s">
+      <c r="A1" s="74" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="73" t="s">
+      <c r="B1" s="74" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="73" t="s">
+      <c r="C1" s="74" t="s">
         <v>2</v>
       </c>
     </row>
     <row r="2" s="2" customFormat="1" ht="45" spans="1:3">
-      <c r="A2" s="74" t="s">
+      <c r="A2" s="75" t="s">
         <v>3</v>
       </c>
-      <c r="B2" s="75" t="s">
+      <c r="B2" s="76" t="s">
         <v>4</v>
       </c>
-      <c r="C2" s="74" t="s">
+      <c r="C2" s="75" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="3" s="2" customFormat="1" ht="60" spans="1:3">
-      <c r="A3" s="74" t="s">
+      <c r="A3" s="75" t="s">
         <v>6</v>
       </c>
-      <c r="B3" s="74" t="s">
+      <c r="B3" s="75" t="s">
         <v>7</v>
       </c>
-      <c r="C3" s="74" t="s">
+      <c r="C3" s="75" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="4" s="2" customFormat="1" ht="30" spans="1:3">
-      <c r="A4" s="74" t="s">
+      <c r="A4" s="75" t="s">
         <v>9</v>
       </c>
-      <c r="B4" s="74" t="s">
+      <c r="B4" s="75" t="s">
         <v>10</v>
       </c>
-      <c r="C4" s="74" t="s">
+      <c r="C4" s="75" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="5" s="2" customFormat="1" spans="1:3">
-      <c r="A5" s="74" t="s">
+      <c r="A5" s="75" t="s">
         <v>12</v>
       </c>
-      <c r="B5" s="74" t="s">
+      <c r="B5" s="75" t="s">
         <v>13</v>
       </c>
-      <c r="C5" s="74" t="s">
+      <c r="C5" s="75" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="6" s="2" customFormat="1" spans="1:3">
-      <c r="A6" s="74" t="s">
+      <c r="A6" s="75" t="s">
         <v>15</v>
       </c>
-      <c r="B6" s="74" t="s">
+      <c r="B6" s="75" t="s">
         <v>16</v>
       </c>
-      <c r="C6" s="74" t="s">
+      <c r="C6" s="75" t="s">
         <v>17</v>
       </c>
     </row>
     <row r="7" s="2" customFormat="1" spans="1:3">
-      <c r="A7" s="74" t="s">
+      <c r="A7" s="75" t="s">
         <v>18</v>
       </c>
-      <c r="B7" s="74" t="s">
+      <c r="B7" s="75" t="s">
         <v>7</v>
       </c>
-      <c r="C7" s="74" t="s">
+      <c r="C7" s="75" t="s">
         <v>19</v>
       </c>
     </row>
     <row r="8" s="2" customFormat="1" ht="13.5" customHeight="1" spans="1:3">
-      <c r="A8" s="74" t="s">
+      <c r="A8" s="75" t="s">
         <v>20</v>
       </c>
-      <c r="B8" s="74" t="s">
+      <c r="B8" s="75" t="s">
         <v>21</v>
       </c>
-      <c r="C8" s="74" t="s">
+      <c r="C8" s="75" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="9" s="2" customFormat="1" spans="1:3">
-      <c r="A9" s="74" t="s">
+      <c r="A9" s="75" t="s">
         <v>23</v>
       </c>
-      <c r="B9" s="74" t="s">
+      <c r="B9" s="75" t="s">
         <v>24</v>
       </c>
-      <c r="C9" s="74" t="s">
+      <c r="C9" s="75" t="s">
         <v>25</v>
       </c>
     </row>
     <row r="10" s="2" customFormat="1" ht="30" spans="1:3">
-      <c r="A10" s="74" t="s">
+      <c r="A10" s="75" t="s">
         <v>26</v>
       </c>
-      <c r="B10" s="74" t="s">
+      <c r="B10" s="75" t="s">
         <v>27</v>
       </c>
-      <c r="C10" s="74" t="s">
+      <c r="C10" s="75" t="s">
         <v>28</v>
       </c>
     </row>
     <row r="11" s="2" customFormat="1" spans="1:3">
-      <c r="A11" s="41"/>
-      <c r="B11" s="41"/>
-      <c r="C11" s="41"/>
+      <c r="A11" s="44"/>
+      <c r="B11" s="44"/>
+      <c r="C11" s="44"/>
     </row>
     <row r="12" s="2" customFormat="1" spans="1:3">
-      <c r="A12" s="41"/>
-      <c r="B12" s="41"/>
-      <c r="C12" s="41"/>
+      <c r="A12" s="44"/>
+      <c r="B12" s="44"/>
+      <c r="C12" s="44"/>
     </row>
     <row r="13" s="2" customFormat="1" spans="1:3">
-      <c r="A13" s="41"/>
-      <c r="B13" s="41"/>
-      <c r="C13" s="41"/>
+      <c r="A13" s="44"/>
+      <c r="B13" s="44"/>
+      <c r="C13" s="44"/>
     </row>
     <row r="14" spans="1:3">
-      <c r="A14" s="41"/>
-      <c r="B14" s="41"/>
-      <c r="C14" s="41"/>
+      <c r="A14" s="44"/>
+      <c r="B14" s="44"/>
+      <c r="C14" s="44"/>
     </row>
     <row r="15" spans="1:3">
-      <c r="A15" s="41"/>
-      <c r="B15" s="41"/>
-      <c r="C15" s="41"/>
+      <c r="A15" s="44"/>
+      <c r="B15" s="44"/>
+      <c r="C15" s="44"/>
     </row>
     <row r="16" spans="1:3">
-      <c r="A16" s="41"/>
-      <c r="B16" s="41"/>
-      <c r="C16" s="41"/>
+      <c r="A16" s="44"/>
+      <c r="B16" s="44"/>
+      <c r="C16" s="44"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -2173,7 +2191,7 @@
       <c r="G5" s="9"/>
     </row>
     <row r="6" s="1" customFormat="1" spans="1:7">
-      <c r="A6" s="71">
+      <c r="A6" s="72">
         <v>5</v>
       </c>
       <c r="B6" s="9" t="s">
@@ -2277,13 +2295,13 @@
       <c r="G11" s="18"/>
     </row>
     <row r="12" spans="1:7">
-      <c r="A12" s="72"/>
-      <c r="B12" s="72"/>
-      <c r="C12" s="72"/>
-      <c r="D12" s="72"/>
-      <c r="E12" s="72"/>
-      <c r="F12" s="72"/>
-      <c r="G12" s="72"/>
+      <c r="A12" s="73"/>
+      <c r="B12" s="73"/>
+      <c r="C12" s="73"/>
+      <c r="D12" s="73"/>
+      <c r="E12" s="73"/>
+      <c r="F12" s="73"/>
+      <c r="G12" s="73"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -2297,331 +2315,331 @@
   <dimension ref="A1:F25"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" outlineLevelCol="5"/>
   <cols>
-    <col min="1" max="2" width="9" style="48"/>
-    <col min="3" max="3" width="15" style="48" customWidth="1"/>
-    <col min="4" max="4" width="23.5" style="48" customWidth="1"/>
-    <col min="5" max="5" width="9" style="48"/>
-    <col min="6" max="6" width="21.875" style="48" customWidth="1"/>
-    <col min="7" max="16384" width="9" style="48"/>
+    <col min="1" max="2" width="9" style="52"/>
+    <col min="3" max="3" width="15" style="52" customWidth="1"/>
+    <col min="4" max="4" width="23.5" style="52" customWidth="1"/>
+    <col min="5" max="5" width="9" style="52"/>
+    <col min="6" max="6" width="21.875" style="52" customWidth="1"/>
+    <col min="7" max="16384" width="9" style="52"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6">
-      <c r="A1" s="49">
+      <c r="A1" s="53">
         <v>1</v>
       </c>
-      <c r="B1" s="50" t="s">
+      <c r="B1" s="54" t="s">
         <v>30</v>
       </c>
-      <c r="C1" s="51"/>
-      <c r="D1" s="52" t="s">
+      <c r="C1" s="55"/>
+      <c r="D1" s="56" t="s">
         <v>51</v>
       </c>
-      <c r="E1" s="65" t="s">
+      <c r="E1" s="68" t="s">
         <v>52</v>
       </c>
-      <c r="F1" s="66" t="s">
+      <c r="F1" s="69" t="s">
         <v>53</v>
       </c>
     </row>
     <row r="2" spans="1:6">
-      <c r="A2" s="53"/>
-      <c r="B2" s="50" t="s">
+      <c r="A2" s="57"/>
+      <c r="B2" s="54" t="s">
         <v>54</v>
       </c>
-      <c r="C2" s="51"/>
-      <c r="D2" s="52" t="s">
+      <c r="C2" s="55"/>
+      <c r="D2" s="56" t="s">
         <v>55</v>
       </c>
-      <c r="E2" s="50" t="s">
+      <c r="E2" s="54" t="s">
         <v>56</v>
       </c>
-      <c r="F2" s="58"/>
+      <c r="F2" s="62"/>
     </row>
     <row r="3" spans="1:6">
-      <c r="A3" s="53"/>
-      <c r="B3" s="50" t="s">
+      <c r="A3" s="57"/>
+      <c r="B3" s="54" t="s">
         <v>57</v>
       </c>
-      <c r="C3" s="51"/>
-      <c r="D3" s="27" t="s">
+      <c r="C3" s="55"/>
+      <c r="D3" s="38" t="s">
         <v>58</v>
       </c>
-      <c r="E3" s="28"/>
-      <c r="F3" s="36"/>
+      <c r="E3" s="39"/>
+      <c r="F3" s="48"/>
     </row>
     <row r="4" spans="1:6">
-      <c r="A4" s="53"/>
-      <c r="B4" s="54" t="s">
+      <c r="A4" s="57"/>
+      <c r="B4" s="58" t="s">
         <v>59</v>
       </c>
-      <c r="C4" s="55"/>
-      <c r="D4" s="55"/>
-      <c r="E4" s="55"/>
-      <c r="F4" s="67"/>
+      <c r="C4" s="59"/>
+      <c r="D4" s="59"/>
+      <c r="E4" s="59"/>
+      <c r="F4" s="70"/>
     </row>
     <row r="5" spans="1:6">
-      <c r="A5" s="53"/>
-      <c r="B5" s="56" t="s">
+      <c r="A5" s="57"/>
+      <c r="B5" s="60" t="s">
         <v>29</v>
       </c>
-      <c r="C5" s="57" t="s">
+      <c r="C5" s="61" t="s">
         <v>60</v>
       </c>
-      <c r="D5" s="57" t="s">
+      <c r="D5" s="61" t="s">
         <v>30</v>
       </c>
-      <c r="E5" s="57" t="s">
+      <c r="E5" s="61" t="s">
         <v>56</v>
       </c>
-      <c r="F5" s="57" t="s">
+      <c r="F5" s="61" t="s">
         <v>57</v>
       </c>
     </row>
     <row r="6" spans="1:6">
-      <c r="A6" s="53"/>
-      <c r="B6" s="58">
+      <c r="A6" s="57"/>
+      <c r="B6" s="62">
         <v>1</v>
       </c>
-      <c r="C6" s="58" t="s">
+      <c r="C6" s="62" t="s">
         <v>61</v>
       </c>
-      <c r="D6" s="59" t="s">
+      <c r="D6" s="63" t="s">
         <v>62</v>
       </c>
-      <c r="E6" s="59"/>
-      <c r="F6" s="59"/>
+      <c r="E6" s="63"/>
+      <c r="F6" s="63"/>
     </row>
     <row r="7" spans="1:6">
-      <c r="A7" s="53"/>
-      <c r="B7" s="58">
+      <c r="A7" s="57"/>
+      <c r="B7" s="62">
         <v>2</v>
       </c>
-      <c r="C7" s="58" t="s">
+      <c r="C7" s="62" t="s">
         <v>63</v>
       </c>
-      <c r="D7" s="59" t="s">
+      <c r="D7" s="63" t="s">
         <v>64</v>
       </c>
-      <c r="E7" s="59"/>
-      <c r="F7" s="59"/>
+      <c r="E7" s="63"/>
+      <c r="F7" s="63"/>
     </row>
     <row r="8" spans="1:6">
-      <c r="A8" s="53"/>
-      <c r="B8" s="58">
+      <c r="A8" s="57"/>
+      <c r="B8" s="62">
         <v>3</v>
       </c>
-      <c r="C8" s="58" t="s">
+      <c r="C8" s="62" t="s">
         <v>65</v>
       </c>
-      <c r="D8" s="59" t="s">
+      <c r="D8" s="63" t="s">
         <v>66</v>
       </c>
-      <c r="E8" s="59"/>
-      <c r="F8" s="59"/>
+      <c r="E8" s="63"/>
+      <c r="F8" s="63"/>
     </row>
     <row r="9" ht="15" spans="1:6">
-      <c r="A9" s="53"/>
-      <c r="B9" s="58"/>
-      <c r="C9" s="60"/>
-      <c r="D9" s="59"/>
-      <c r="E9" s="59"/>
-      <c r="F9" s="59"/>
+      <c r="A9" s="57"/>
+      <c r="B9" s="62"/>
+      <c r="C9" s="64"/>
+      <c r="D9" s="63"/>
+      <c r="E9" s="63"/>
+      <c r="F9" s="63"/>
     </row>
     <row r="10" spans="1:6">
-      <c r="A10" s="61"/>
-      <c r="B10" s="62"/>
-      <c r="C10" s="63"/>
-      <c r="D10" s="63"/>
-      <c r="E10" s="63"/>
-      <c r="F10" s="68"/>
+      <c r="A10" s="65"/>
+      <c r="B10" s="66"/>
+      <c r="C10" s="67"/>
+      <c r="D10" s="67"/>
+      <c r="E10" s="67"/>
+      <c r="F10" s="71"/>
     </row>
     <row r="11" spans="1:6">
-      <c r="A11" s="49">
+      <c r="A11" s="53">
         <v>2</v>
       </c>
-      <c r="B11" s="50" t="s">
+      <c r="B11" s="54" t="s">
         <v>30</v>
       </c>
-      <c r="C11" s="51"/>
-      <c r="D11" s="52" t="s">
+      <c r="C11" s="55"/>
+      <c r="D11" s="56" t="s">
         <v>67</v>
       </c>
-      <c r="E11" s="65" t="s">
+      <c r="E11" s="68" t="s">
         <v>52</v>
       </c>
-      <c r="F11" s="66" t="s">
+      <c r="F11" s="69" t="s">
         <v>53</v>
       </c>
     </row>
     <row r="12" spans="1:6">
-      <c r="A12" s="53"/>
-      <c r="B12" s="50" t="s">
+      <c r="A12" s="57"/>
+      <c r="B12" s="54" t="s">
         <v>54</v>
       </c>
-      <c r="C12" s="51"/>
-      <c r="D12" s="52" t="s">
+      <c r="C12" s="55"/>
+      <c r="D12" s="56" t="s">
         <v>68</v>
       </c>
-      <c r="E12" s="50" t="s">
+      <c r="E12" s="54" t="s">
         <v>56</v>
       </c>
-      <c r="F12" s="58"/>
+      <c r="F12" s="62"/>
     </row>
     <row r="13" ht="33" customHeight="1" spans="1:6">
-      <c r="A13" s="53"/>
-      <c r="B13" s="50" t="s">
+      <c r="A13" s="57"/>
+      <c r="B13" s="54" t="s">
         <v>57</v>
       </c>
-      <c r="C13" s="51"/>
-      <c r="D13" s="64" t="s">
+      <c r="C13" s="55"/>
+      <c r="D13" s="28" t="s">
         <v>69</v>
       </c>
-      <c r="E13" s="69"/>
-      <c r="F13" s="70"/>
+      <c r="E13" s="29"/>
+      <c r="F13" s="37"/>
     </row>
     <row r="14" spans="1:6">
-      <c r="A14" s="53"/>
-      <c r="B14" s="54" t="s">
+      <c r="A14" s="57"/>
+      <c r="B14" s="58" t="s">
         <v>59</v>
       </c>
-      <c r="C14" s="55"/>
-      <c r="D14" s="55"/>
-      <c r="E14" s="55"/>
-      <c r="F14" s="67"/>
+      <c r="C14" s="59"/>
+      <c r="D14" s="59"/>
+      <c r="E14" s="59"/>
+      <c r="F14" s="70"/>
     </row>
     <row r="15" spans="1:6">
-      <c r="A15" s="53"/>
-      <c r="B15" s="56" t="s">
+      <c r="A15" s="57"/>
+      <c r="B15" s="60" t="s">
         <v>29</v>
       </c>
-      <c r="C15" s="57" t="s">
+      <c r="C15" s="61" t="s">
         <v>60</v>
       </c>
-      <c r="D15" s="57" t="s">
+      <c r="D15" s="61" t="s">
         <v>30</v>
       </c>
-      <c r="E15" s="57" t="s">
+      <c r="E15" s="61" t="s">
         <v>56</v>
       </c>
-      <c r="F15" s="57" t="s">
+      <c r="F15" s="61" t="s">
         <v>57</v>
       </c>
     </row>
     <row r="16" spans="1:6">
-      <c r="A16" s="53"/>
-      <c r="B16" s="58">
+      <c r="A16" s="57"/>
+      <c r="B16" s="62">
         <v>1</v>
       </c>
-      <c r="C16" s="58" t="s">
+      <c r="C16" s="62" t="s">
         <v>61</v>
       </c>
-      <c r="D16" s="59" t="s">
+      <c r="D16" s="63" t="s">
         <v>62</v>
       </c>
-      <c r="E16" s="59"/>
-      <c r="F16" s="59"/>
+      <c r="E16" s="63"/>
+      <c r="F16" s="63"/>
     </row>
     <row r="17" spans="1:6">
-      <c r="A17" s="53"/>
-      <c r="B17" s="58">
+      <c r="A17" s="57"/>
+      <c r="B17" s="62">
         <v>2</v>
       </c>
-      <c r="C17" s="58" t="s">
+      <c r="C17" s="62" t="s">
         <v>70</v>
       </c>
-      <c r="D17" s="59" t="s">
+      <c r="D17" s="63" t="s">
         <v>71</v>
       </c>
-      <c r="E17" s="59"/>
-      <c r="F17" s="59"/>
+      <c r="E17" s="63"/>
+      <c r="F17" s="63"/>
     </row>
     <row r="18" spans="1:6">
-      <c r="A18" s="53"/>
-      <c r="B18" s="58">
+      <c r="A18" s="57"/>
+      <c r="B18" s="62">
         <v>3</v>
       </c>
-      <c r="C18" s="58" t="s">
+      <c r="C18" s="62" t="s">
         <v>72</v>
       </c>
-      <c r="D18" s="59" t="s">
+      <c r="D18" s="63" t="s">
         <v>73</v>
       </c>
-      <c r="E18" s="59"/>
-      <c r="F18" s="59"/>
+      <c r="E18" s="63"/>
+      <c r="F18" s="63"/>
     </row>
     <row r="19" spans="1:6">
-      <c r="A19" s="53"/>
-      <c r="B19" s="58">
+      <c r="A19" s="57"/>
+      <c r="B19" s="62">
         <v>4</v>
       </c>
-      <c r="C19" s="58" t="s">
+      <c r="C19" s="62" t="s">
         <v>74</v>
       </c>
-      <c r="D19" s="59" t="s">
+      <c r="D19" s="63" t="s">
         <v>75</v>
       </c>
-      <c r="E19" s="59"/>
-      <c r="F19" s="59"/>
+      <c r="E19" s="63"/>
+      <c r="F19" s="63"/>
     </row>
     <row r="20" spans="1:6">
-      <c r="A20" s="53"/>
-      <c r="B20" s="58">
+      <c r="A20" s="57"/>
+      <c r="B20" s="62">
         <v>5</v>
       </c>
-      <c r="C20" s="58" t="s">
+      <c r="C20" s="62" t="s">
         <v>76</v>
       </c>
-      <c r="D20" s="59" t="s">
+      <c r="D20" s="63" t="s">
         <v>77</v>
       </c>
-      <c r="E20" s="59"/>
-      <c r="F20" s="59"/>
+      <c r="E20" s="63"/>
+      <c r="F20" s="63"/>
     </row>
     <row r="21" spans="1:6">
-      <c r="A21" s="53"/>
-      <c r="B21" s="58">
+      <c r="A21" s="57"/>
+      <c r="B21" s="62">
         <v>6</v>
       </c>
-      <c r="C21" s="58" t="s">
+      <c r="C21" s="62" t="s">
         <v>78</v>
       </c>
-      <c r="D21" s="59" t="s">
+      <c r="D21" s="63" t="s">
         <v>79</v>
       </c>
-      <c r="E21" s="59"/>
-      <c r="F21" s="59"/>
+      <c r="E21" s="63"/>
+      <c r="F21" s="63"/>
     </row>
     <row r="22" spans="1:6">
-      <c r="A22" s="53"/>
-      <c r="B22" s="58"/>
-      <c r="C22" s="58"/>
-      <c r="D22" s="59"/>
-      <c r="E22" s="59"/>
-      <c r="F22" s="59"/>
+      <c r="A22" s="57"/>
+      <c r="B22" s="62"/>
+      <c r="C22" s="62"/>
+      <c r="D22" s="63"/>
+      <c r="E22" s="63"/>
+      <c r="F22" s="63"/>
     </row>
     <row r="23" spans="1:6">
-      <c r="A23" s="53"/>
-      <c r="B23" s="58"/>
-      <c r="C23" s="58"/>
-      <c r="D23" s="59"/>
-      <c r="E23" s="59"/>
-      <c r="F23" s="59"/>
+      <c r="A23" s="57"/>
+      <c r="B23" s="62"/>
+      <c r="C23" s="62"/>
+      <c r="D23" s="63"/>
+      <c r="E23" s="63"/>
+      <c r="F23" s="63"/>
     </row>
     <row r="24" ht="15" spans="1:6">
-      <c r="A24" s="53"/>
-      <c r="B24" s="58"/>
-      <c r="C24" s="60"/>
-      <c r="D24" s="59"/>
-      <c r="E24" s="59"/>
-      <c r="F24" s="59"/>
+      <c r="A24" s="57"/>
+      <c r="B24" s="62"/>
+      <c r="C24" s="64"/>
+      <c r="D24" s="63"/>
+      <c r="E24" s="63"/>
+      <c r="F24" s="63"/>
     </row>
     <row r="25" spans="1:6">
-      <c r="A25" s="61"/>
-      <c r="B25" s="62"/>
-      <c r="C25" s="63"/>
-      <c r="D25" s="63"/>
-      <c r="E25" s="63"/>
-      <c r="F25" s="68"/>
+      <c r="A25" s="65"/>
+      <c r="B25" s="66"/>
+      <c r="C25" s="67"/>
+      <c r="D25" s="67"/>
+      <c r="E25" s="67"/>
+      <c r="F25" s="71"/>
     </row>
   </sheetData>
   <mergeCells count="14">
@@ -2682,13 +2700,13 @@
       <c r="H1" s="6" t="s">
         <v>83</v>
       </c>
-      <c r="I1" s="24"/>
-      <c r="J1" s="24"/>
-      <c r="K1" s="24"/>
-      <c r="L1" s="24"/>
-      <c r="M1" s="24"/>
-      <c r="N1" s="24"/>
-      <c r="O1" s="29"/>
+      <c r="I1" s="25"/>
+      <c r="J1" s="25"/>
+      <c r="K1" s="25"/>
+      <c r="L1" s="25"/>
+      <c r="M1" s="25"/>
+      <c r="N1" s="25"/>
+      <c r="O1" s="30"/>
     </row>
     <row r="2" s="1" customFormat="1" spans="1:15">
       <c r="A2" s="4" t="s">
@@ -2705,13 +2723,13 @@
         <v>85</v>
       </c>
       <c r="H2" s="6"/>
-      <c r="I2" s="24"/>
-      <c r="J2" s="24"/>
-      <c r="K2" s="24"/>
-      <c r="L2" s="24"/>
-      <c r="M2" s="24"/>
-      <c r="N2" s="24"/>
-      <c r="O2" s="29"/>
+      <c r="I2" s="25"/>
+      <c r="J2" s="25"/>
+      <c r="K2" s="25"/>
+      <c r="L2" s="25"/>
+      <c r="M2" s="25"/>
+      <c r="N2" s="25"/>
+      <c r="O2" s="30"/>
     </row>
     <row r="3" s="1" customFormat="1" spans="1:15">
       <c r="A3" s="4" t="s">
@@ -2726,13 +2744,13 @@
         <v>86</v>
       </c>
       <c r="H3" s="6"/>
-      <c r="I3" s="24"/>
-      <c r="J3" s="24"/>
-      <c r="K3" s="24"/>
-      <c r="L3" s="24"/>
-      <c r="M3" s="24"/>
-      <c r="N3" s="24"/>
-      <c r="O3" s="29"/>
+      <c r="I3" s="25"/>
+      <c r="J3" s="25"/>
+      <c r="K3" s="25"/>
+      <c r="L3" s="25"/>
+      <c r="M3" s="25"/>
+      <c r="N3" s="25"/>
+      <c r="O3" s="30"/>
     </row>
     <row r="4" s="1" customFormat="1" spans="1:15">
       <c r="A4" s="4" t="s">
@@ -2741,17 +2759,17 @@
       <c r="B4" s="4"/>
       <c r="C4" s="4"/>
       <c r="D4" s="6"/>
-      <c r="E4" s="24"/>
-      <c r="F4" s="24"/>
-      <c r="G4" s="24"/>
-      <c r="H4" s="24"/>
-      <c r="I4" s="24"/>
-      <c r="J4" s="24"/>
-      <c r="K4" s="24"/>
-      <c r="L4" s="24"/>
-      <c r="M4" s="24"/>
-      <c r="N4" s="24"/>
-      <c r="O4" s="29"/>
+      <c r="E4" s="25"/>
+      <c r="F4" s="25"/>
+      <c r="G4" s="25"/>
+      <c r="H4" s="25"/>
+      <c r="I4" s="25"/>
+      <c r="J4" s="25"/>
+      <c r="K4" s="25"/>
+      <c r="L4" s="25"/>
+      <c r="M4" s="25"/>
+      <c r="N4" s="25"/>
+      <c r="O4" s="30"/>
     </row>
     <row r="5" s="1" customFormat="1" spans="1:15">
       <c r="A5" s="7"/>
@@ -2857,16 +2875,16 @@
       <c r="H8" s="9" t="s">
         <v>102</v>
       </c>
-      <c r="I8" s="30" t="s">
+      <c r="I8" s="31" t="s">
         <v>37</v>
       </c>
-      <c r="J8" s="31">
+      <c r="J8" s="32">
         <v>50</v>
       </c>
       <c r="K8" s="9"/>
-      <c r="L8" s="32"/>
+      <c r="L8" s="33"/>
       <c r="M8" s="5"/>
-      <c r="N8" s="32"/>
+      <c r="N8" s="33"/>
       <c r="O8" s="9"/>
     </row>
     <row r="9" s="2" customFormat="1" ht="15" spans="1:15">
@@ -2875,28 +2893,28 @@
       </c>
       <c r="B9" s="10"/>
       <c r="C9" s="10"/>
-      <c r="D9" s="42" t="s">
+      <c r="D9" s="45" t="s">
         <v>103</v>
       </c>
-      <c r="E9" s="42"/>
-      <c r="F9" s="42" t="s">
+      <c r="E9" s="45"/>
+      <c r="F9" s="45" t="s">
         <v>104</v>
       </c>
-      <c r="G9" s="42"/>
+      <c r="G9" s="45"/>
       <c r="H9" s="9" t="s">
         <v>102</v>
       </c>
-      <c r="I9" s="30" t="s">
+      <c r="I9" s="31" t="s">
         <v>37</v>
       </c>
-      <c r="J9" s="31">
+      <c r="J9" s="32">
         <v>100</v>
       </c>
       <c r="K9" s="10"/>
-      <c r="L9" s="33"/>
-      <c r="M9" s="42"/>
-      <c r="N9" s="33"/>
-      <c r="O9" s="41"/>
+      <c r="L9" s="34"/>
+      <c r="M9" s="45"/>
+      <c r="N9" s="34"/>
+      <c r="O9" s="44"/>
     </row>
     <row r="10" s="1" customFormat="1" ht="15" spans="1:15">
       <c r="A10" s="9">
@@ -2915,16 +2933,16 @@
       <c r="H10" s="9" t="s">
         <v>102</v>
       </c>
-      <c r="I10" s="30" t="s">
+      <c r="I10" s="31" t="s">
         <v>37</v>
       </c>
-      <c r="J10" s="31">
+      <c r="J10" s="32">
         <v>100</v>
       </c>
       <c r="K10" s="9"/>
-      <c r="L10" s="32"/>
+      <c r="L10" s="33"/>
       <c r="M10" s="5"/>
-      <c r="N10" s="32"/>
+      <c r="N10" s="33"/>
       <c r="O10" s="9"/>
     </row>
     <row r="11" s="1" customFormat="1" ht="15" spans="1:15">
@@ -2942,20 +2960,20 @@
       </c>
       <c r="G11" s="5"/>
       <c r="H11" s="9"/>
-      <c r="I11" s="30" t="s">
+      <c r="I11" s="31" t="s">
         <v>37</v>
       </c>
-      <c r="J11" s="31">
+      <c r="J11" s="32">
         <v>100</v>
       </c>
       <c r="K11" s="9"/>
-      <c r="L11" s="32" t="s">
+      <c r="L11" s="33" t="s">
         <v>51</v>
       </c>
       <c r="M11" s="5" t="s">
         <v>61</v>
       </c>
-      <c r="N11" s="32"/>
+      <c r="N11" s="33"/>
       <c r="O11" s="9"/>
     </row>
     <row r="12" s="1" customFormat="1" ht="27" spans="1:15">
@@ -2973,15 +2991,15 @@
       </c>
       <c r="G12" s="5"/>
       <c r="H12" s="9"/>
-      <c r="I12" s="30" t="s">
+      <c r="I12" s="31" t="s">
+        <v>40</v>
+      </c>
+      <c r="J12" s="32"/>
+      <c r="K12" s="9"/>
+      <c r="L12" s="33"/>
+      <c r="M12" s="5"/>
+      <c r="N12" s="33" t="s">
         <v>110</v>
-      </c>
-      <c r="J12" s="31"/>
-      <c r="K12" s="9"/>
-      <c r="L12" s="32"/>
-      <c r="M12" s="5"/>
-      <c r="N12" s="32" t="s">
-        <v>111</v>
       </c>
       <c r="O12" s="9"/>
     </row>
@@ -2992,24 +3010,24 @@
       <c r="B13" s="9"/>
       <c r="C13" s="9"/>
       <c r="D13" s="5" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="E13" s="9"/>
       <c r="F13" s="5" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="G13" s="5"/>
       <c r="H13" s="9"/>
-      <c r="I13" s="30" t="s">
+      <c r="I13" s="31" t="s">
         <v>37</v>
       </c>
-      <c r="J13" s="31">
+      <c r="J13" s="32">
         <v>50</v>
       </c>
       <c r="K13" s="9"/>
-      <c r="L13" s="32"/>
+      <c r="L13" s="33"/>
       <c r="M13" s="5"/>
-      <c r="N13" s="32"/>
+      <c r="N13" s="33"/>
       <c r="O13" s="9"/>
     </row>
     <row r="14" s="1" customFormat="1" ht="40.5" spans="1:15">
@@ -3019,43 +3037,57 @@
       <c r="B14" s="9"/>
       <c r="C14" s="9"/>
       <c r="D14" s="5" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="E14" s="9"/>
       <c r="F14" s="5" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="G14" s="5"/>
       <c r="H14" s="9" t="s">
         <v>102</v>
       </c>
-      <c r="I14" s="30" t="s">
-        <v>116</v>
-      </c>
-      <c r="J14" s="31"/>
+      <c r="I14" s="31" t="s">
+        <v>46</v>
+      </c>
+      <c r="J14" s="32"/>
       <c r="K14" s="9"/>
-      <c r="L14" s="32"/>
+      <c r="L14" s="33"/>
       <c r="M14" s="5"/>
-      <c r="N14" s="32" t="s">
-        <v>117</v>
+      <c r="N14" s="33" t="s">
+        <v>115</v>
       </c>
       <c r="O14" s="9"/>
     </row>
     <row r="15" s="1" customFormat="1" ht="15" spans="1:15">
-      <c r="A15" s="9"/>
+      <c r="A15" s="9">
+        <v>8</v>
+      </c>
       <c r="B15" s="9"/>
       <c r="C15" s="9"/>
-      <c r="D15" s="5"/>
+      <c r="D15" s="5" t="s">
+        <v>116</v>
+      </c>
       <c r="E15" s="9"/>
-      <c r="F15" s="5"/>
-      <c r="G15" s="5"/>
-      <c r="H15" s="9"/>
-      <c r="I15" s="34"/>
-      <c r="J15" s="31"/>
+      <c r="F15" s="5" t="s">
+        <v>117</v>
+      </c>
+      <c r="G15" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="H15" s="9" t="s">
+        <v>102</v>
+      </c>
+      <c r="I15" s="35" t="s">
+        <v>46</v>
+      </c>
+      <c r="J15" s="32"/>
       <c r="K15" s="9"/>
-      <c r="L15" s="32"/>
+      <c r="L15" s="33"/>
       <c r="M15" s="5"/>
-      <c r="N15" s="32"/>
+      <c r="N15" s="33" t="s">
+        <v>118</v>
+      </c>
       <c r="O15" s="9"/>
     </row>
     <row r="16" s="1" customFormat="1" ht="15" spans="1:15">
@@ -3067,12 +3099,12 @@
       <c r="F16" s="5"/>
       <c r="G16" s="5"/>
       <c r="H16" s="9"/>
-      <c r="I16" s="34"/>
-      <c r="J16" s="31"/>
+      <c r="I16" s="35"/>
+      <c r="J16" s="32"/>
       <c r="K16" s="9"/>
-      <c r="L16" s="32"/>
+      <c r="L16" s="33"/>
       <c r="M16" s="5"/>
-      <c r="N16" s="32"/>
+      <c r="N16" s="33"/>
       <c r="O16" s="9"/>
     </row>
     <row r="17" s="1" customFormat="1" ht="15" spans="1:15">
@@ -3084,12 +3116,12 @@
       <c r="F17" s="5"/>
       <c r="G17" s="5"/>
       <c r="H17" s="9"/>
-      <c r="I17" s="34"/>
-      <c r="J17" s="31"/>
+      <c r="I17" s="35"/>
+      <c r="J17" s="32"/>
       <c r="K17" s="9"/>
-      <c r="L17" s="32"/>
+      <c r="L17" s="33"/>
       <c r="M17" s="5"/>
-      <c r="N17" s="32"/>
+      <c r="N17" s="33"/>
       <c r="O17" s="9"/>
     </row>
     <row r="18" s="1" customFormat="1" ht="15" spans="1:15">
@@ -3101,12 +3133,12 @@
       <c r="F18" s="5"/>
       <c r="G18" s="5"/>
       <c r="H18" s="9"/>
-      <c r="I18" s="34"/>
-      <c r="J18" s="31"/>
+      <c r="I18" s="35"/>
+      <c r="J18" s="32"/>
       <c r="K18" s="9"/>
-      <c r="L18" s="32"/>
+      <c r="L18" s="33"/>
       <c r="M18" s="5"/>
-      <c r="N18" s="32"/>
+      <c r="N18" s="33"/>
       <c r="O18" s="9"/>
     </row>
     <row r="19" s="1" customFormat="1" ht="15" spans="1:15">
@@ -3118,12 +3150,12 @@
       <c r="F19" s="5"/>
       <c r="G19" s="5"/>
       <c r="H19" s="9"/>
-      <c r="I19" s="34"/>
-      <c r="J19" s="31"/>
+      <c r="I19" s="35"/>
+      <c r="J19" s="32"/>
       <c r="K19" s="9"/>
-      <c r="L19" s="32"/>
+      <c r="L19" s="33"/>
       <c r="M19" s="5"/>
-      <c r="N19" s="32"/>
+      <c r="N19" s="33"/>
       <c r="O19" s="9"/>
     </row>
     <row r="20" s="1" customFormat="1" spans="1:15">
@@ -3138,9 +3170,9 @@
       <c r="I20" s="9"/>
       <c r="J20" s="9"/>
       <c r="K20" s="9"/>
-      <c r="L20" s="32"/>
+      <c r="L20" s="33"/>
       <c r="M20" s="5"/>
-      <c r="N20" s="32"/>
+      <c r="N20" s="33"/>
       <c r="O20" s="9"/>
     </row>
     <row r="21" s="3" customFormat="1" spans="1:15">
@@ -3158,11 +3190,11 @@
       <c r="L21" s="12"/>
       <c r="M21" s="12"/>
       <c r="N21" s="12"/>
-      <c r="O21" s="43"/>
+      <c r="O21" s="46"/>
     </row>
     <row r="22" s="3" customFormat="1" spans="1:15">
       <c r="A22" s="13" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="B22" s="14"/>
       <c r="C22" s="14"/>
@@ -3177,14 +3209,14 @@
       <c r="L22" s="14"/>
       <c r="M22" s="14"/>
       <c r="N22" s="14"/>
-      <c r="O22" s="44"/>
+      <c r="O22" s="47"/>
     </row>
     <row r="23" s="3" customFormat="1" spans="1:15">
       <c r="A23" s="15" t="s">
         <v>29</v>
       </c>
       <c r="B23" s="16" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="C23" s="17"/>
       <c r="D23" s="16" t="s">
@@ -3197,17 +3229,17 @@
         <v>56</v>
       </c>
       <c r="G23" s="15" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="H23" s="15"/>
       <c r="I23" s="15"/>
       <c r="J23" s="16" t="s">
-        <v>121</v>
-      </c>
-      <c r="K23" s="35"/>
-      <c r="L23" s="35"/>
-      <c r="M23" s="35"/>
-      <c r="N23" s="35"/>
+        <v>122</v>
+      </c>
+      <c r="K23" s="36"/>
+      <c r="L23" s="36"/>
+      <c r="M23" s="36"/>
+      <c r="N23" s="36"/>
       <c r="O23" s="17"/>
     </row>
     <row r="24" s="3" customFormat="1" spans="1:15">
@@ -3215,89 +3247,89 @@
       <c r="B24" s="18"/>
       <c r="C24" s="18"/>
       <c r="D24" s="18"/>
-      <c r="E24" s="26"/>
-      <c r="F24" s="26"/>
-      <c r="G24" s="27"/>
-      <c r="H24" s="28"/>
-      <c r="I24" s="36"/>
-      <c r="J24" s="27"/>
-      <c r="K24" s="28"/>
-      <c r="L24" s="28"/>
-      <c r="M24" s="28"/>
-      <c r="N24" s="28"/>
-      <c r="O24" s="36"/>
+      <c r="E24" s="27"/>
+      <c r="F24" s="27"/>
+      <c r="G24" s="38"/>
+      <c r="H24" s="39"/>
+      <c r="I24" s="48"/>
+      <c r="J24" s="38"/>
+      <c r="K24" s="39"/>
+      <c r="L24" s="39"/>
+      <c r="M24" s="39"/>
+      <c r="N24" s="39"/>
+      <c r="O24" s="48"/>
     </row>
     <row r="25" s="3" customFormat="1" spans="1:15">
       <c r="A25" s="18"/>
       <c r="B25" s="18"/>
       <c r="C25" s="18"/>
       <c r="D25" s="18"/>
-      <c r="E25" s="26"/>
-      <c r="F25" s="26"/>
-      <c r="G25" s="27"/>
-      <c r="H25" s="28"/>
-      <c r="I25" s="36"/>
-      <c r="J25" s="27"/>
-      <c r="K25" s="28"/>
-      <c r="L25" s="28"/>
-      <c r="M25" s="28"/>
-      <c r="N25" s="28"/>
-      <c r="O25" s="36"/>
+      <c r="E25" s="27"/>
+      <c r="F25" s="27"/>
+      <c r="G25" s="38"/>
+      <c r="H25" s="39"/>
+      <c r="I25" s="48"/>
+      <c r="J25" s="38"/>
+      <c r="K25" s="39"/>
+      <c r="L25" s="39"/>
+      <c r="M25" s="39"/>
+      <c r="N25" s="39"/>
+      <c r="O25" s="48"/>
     </row>
     <row r="26" s="3" customFormat="1" spans="1:15">
       <c r="A26" s="18"/>
       <c r="B26" s="18"/>
       <c r="C26" s="18"/>
       <c r="D26" s="18"/>
-      <c r="E26" s="26"/>
-      <c r="F26" s="26"/>
-      <c r="G26" s="27"/>
-      <c r="H26" s="28"/>
-      <c r="I26" s="36"/>
-      <c r="J26" s="27"/>
-      <c r="K26" s="28"/>
-      <c r="L26" s="28"/>
-      <c r="M26" s="28"/>
-      <c r="N26" s="28"/>
-      <c r="O26" s="36"/>
+      <c r="E26" s="27"/>
+      <c r="F26" s="27"/>
+      <c r="G26" s="38"/>
+      <c r="H26" s="39"/>
+      <c r="I26" s="48"/>
+      <c r="J26" s="38"/>
+      <c r="K26" s="39"/>
+      <c r="L26" s="39"/>
+      <c r="M26" s="39"/>
+      <c r="N26" s="39"/>
+      <c r="O26" s="48"/>
     </row>
     <row r="27" s="3" customFormat="1" spans="1:15">
       <c r="A27" s="18"/>
       <c r="B27" s="18"/>
       <c r="C27" s="18"/>
       <c r="D27" s="18"/>
-      <c r="E27" s="26"/>
-      <c r="F27" s="26"/>
-      <c r="G27" s="27"/>
-      <c r="H27" s="28"/>
-      <c r="I27" s="36"/>
-      <c r="J27" s="27"/>
-      <c r="K27" s="28"/>
-      <c r="L27" s="28"/>
-      <c r="M27" s="28"/>
-      <c r="N27" s="28"/>
-      <c r="O27" s="36"/>
+      <c r="E27" s="27"/>
+      <c r="F27" s="27"/>
+      <c r="G27" s="38"/>
+      <c r="H27" s="39"/>
+      <c r="I27" s="48"/>
+      <c r="J27" s="38"/>
+      <c r="K27" s="39"/>
+      <c r="L27" s="39"/>
+      <c r="M27" s="39"/>
+      <c r="N27" s="39"/>
+      <c r="O27" s="48"/>
     </row>
     <row r="28" s="1" customFormat="1" spans="1:15">
-      <c r="A28" s="19"/>
-      <c r="B28" s="20"/>
-      <c r="C28" s="20"/>
-      <c r="D28" s="20"/>
-      <c r="E28" s="20"/>
-      <c r="F28" s="20"/>
-      <c r="G28" s="20"/>
-      <c r="H28" s="20"/>
-      <c r="I28" s="20"/>
-      <c r="J28" s="20"/>
-      <c r="K28" s="20"/>
-      <c r="L28" s="20"/>
-      <c r="M28" s="20"/>
-      <c r="N28" s="20"/>
-      <c r="O28" s="45"/>
+      <c r="A28" s="20"/>
+      <c r="B28" s="21"/>
+      <c r="C28" s="21"/>
+      <c r="D28" s="21"/>
+      <c r="E28" s="21"/>
+      <c r="F28" s="21"/>
+      <c r="G28" s="21"/>
+      <c r="H28" s="21"/>
+      <c r="I28" s="21"/>
+      <c r="J28" s="21"/>
+      <c r="K28" s="21"/>
+      <c r="L28" s="21"/>
+      <c r="M28" s="21"/>
+      <c r="N28" s="21"/>
+      <c r="O28" s="49"/>
     </row>
     <row r="29" s="1" customFormat="1" spans="1:15">
       <c r="A29" s="8" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="B29" s="8"/>
       <c r="C29" s="8"/>
@@ -3315,21 +3347,21 @@
       <c r="O29" s="8"/>
     </row>
     <row r="30" s="1" customFormat="1" spans="1:15">
-      <c r="A30" s="21"/>
+      <c r="A30" s="22"/>
       <c r="B30" s="4" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="C30" s="4"/>
       <c r="D30" s="5"/>
       <c r="E30" s="5"/>
       <c r="F30" s="4" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="G30" s="5"/>
       <c r="H30" s="5"/>
       <c r="I30" s="5"/>
       <c r="J30" s="4" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="K30" s="4"/>
       <c r="L30" s="5"/>
@@ -3338,7 +3370,7 @@
       <c r="O30" s="5"/>
     </row>
     <row r="31" s="1" customFormat="1" spans="1:15">
-      <c r="A31" s="21"/>
+      <c r="A31" s="22"/>
       <c r="B31" s="4" t="s">
         <v>54</v>
       </c>
@@ -3352,7 +3384,7 @@
       <c r="H31" s="5"/>
       <c r="I31" s="5"/>
       <c r="J31" s="4" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="K31" s="4"/>
       <c r="L31" s="5"/>
@@ -3361,15 +3393,15 @@
       <c r="O31" s="5"/>
     </row>
     <row r="32" s="1" customFormat="1" spans="1:15">
-      <c r="A32" s="21"/>
+      <c r="A32" s="22"/>
       <c r="B32" s="4" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="C32" s="4"/>
       <c r="D32" s="5"/>
       <c r="E32" s="5"/>
       <c r="F32" s="4" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="G32" s="9"/>
       <c r="H32" s="9"/>
@@ -3382,7 +3414,7 @@
       <c r="O32" s="5"/>
     </row>
     <row r="33" s="1" customFormat="1" spans="1:15">
-      <c r="A33" s="21"/>
+      <c r="A33" s="22"/>
       <c r="B33" s="4" t="s">
         <v>87</v>
       </c>
@@ -3403,42 +3435,42 @@
       <c r="O33" s="5"/>
     </row>
     <row r="34" s="1" customFormat="1" spans="1:15">
-      <c r="A34" s="21"/>
-      <c r="B34" s="22" t="s">
-        <v>129</v>
-      </c>
-      <c r="C34" s="22"/>
-      <c r="D34" s="22"/>
-      <c r="E34" s="22"/>
-      <c r="F34" s="22"/>
-      <c r="G34" s="22"/>
-      <c r="H34" s="22"/>
-      <c r="I34" s="22"/>
-      <c r="J34" s="37"/>
-      <c r="K34" s="38"/>
-      <c r="L34" s="37"/>
-      <c r="M34" s="46"/>
-      <c r="N34" s="46"/>
-      <c r="O34" s="38"/>
+      <c r="A34" s="22"/>
+      <c r="B34" s="23" t="s">
+        <v>130</v>
+      </c>
+      <c r="C34" s="23"/>
+      <c r="D34" s="23"/>
+      <c r="E34" s="23"/>
+      <c r="F34" s="23"/>
+      <c r="G34" s="23"/>
+      <c r="H34" s="23"/>
+      <c r="I34" s="23"/>
+      <c r="J34" s="40"/>
+      <c r="K34" s="41"/>
+      <c r="L34" s="40"/>
+      <c r="M34" s="50"/>
+      <c r="N34" s="50"/>
+      <c r="O34" s="41"/>
     </row>
     <row r="35" s="1" customFormat="1" spans="1:15">
-      <c r="A35" s="21"/>
+      <c r="A35" s="22"/>
       <c r="B35" s="4" t="s">
         <v>29</v>
       </c>
       <c r="C35" s="4" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="D35" s="4"/>
       <c r="E35" s="4" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="F35" s="4" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="G35" s="4"/>
       <c r="H35" s="4" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="I35" s="4"/>
       <c r="J35" s="4"/>
@@ -3449,7 +3481,7 @@
       <c r="O35" s="4"/>
     </row>
     <row r="36" s="1" customFormat="1" spans="1:15">
-      <c r="A36" s="21"/>
+      <c r="A36" s="22"/>
       <c r="B36" s="9">
         <v>1</v>
       </c>
@@ -3468,55 +3500,55 @@
       <c r="O36" s="9"/>
     </row>
     <row r="37" s="1" customFormat="1" spans="1:15">
-      <c r="A37" s="23"/>
+      <c r="A37" s="24"/>
       <c r="B37" s="9"/>
       <c r="C37" s="6"/>
-      <c r="D37" s="24"/>
+      <c r="D37" s="25"/>
       <c r="E37" s="5"/>
       <c r="F37" s="6"/>
-      <c r="G37" s="29"/>
+      <c r="G37" s="30"/>
       <c r="H37" s="6"/>
-      <c r="I37" s="29"/>
-      <c r="J37" s="39"/>
-      <c r="K37" s="40"/>
-      <c r="L37" s="39"/>
-      <c r="M37" s="47"/>
-      <c r="N37" s="47"/>
-      <c r="O37" s="40"/>
+      <c r="I37" s="30"/>
+      <c r="J37" s="42"/>
+      <c r="K37" s="43"/>
+      <c r="L37" s="42"/>
+      <c r="M37" s="51"/>
+      <c r="N37" s="51"/>
+      <c r="O37" s="43"/>
     </row>
     <row r="38" s="1" customFormat="1" spans="1:15">
-      <c r="A38" s="25"/>
+      <c r="A38" s="26"/>
       <c r="B38" s="9"/>
       <c r="C38" s="6"/>
-      <c r="D38" s="24"/>
+      <c r="D38" s="25"/>
       <c r="E38" s="5"/>
       <c r="F38" s="6"/>
-      <c r="G38" s="29"/>
+      <c r="G38" s="30"/>
       <c r="H38" s="6"/>
-      <c r="I38" s="29"/>
-      <c r="J38" s="39"/>
-      <c r="K38" s="40"/>
-      <c r="L38" s="39"/>
-      <c r="M38" s="47"/>
-      <c r="N38" s="47"/>
-      <c r="O38" s="40"/>
+      <c r="I38" s="30"/>
+      <c r="J38" s="42"/>
+      <c r="K38" s="43"/>
+      <c r="L38" s="42"/>
+      <c r="M38" s="51"/>
+      <c r="N38" s="51"/>
+      <c r="O38" s="43"/>
     </row>
     <row r="39" s="1" customFormat="1" spans="1:15">
-      <c r="A39" s="21"/>
+      <c r="A39" s="22"/>
       <c r="B39" s="4" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="C39" s="4"/>
       <c r="D39" s="5"/>
       <c r="E39" s="5"/>
       <c r="F39" s="4" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="G39" s="5"/>
       <c r="H39" s="5"/>
       <c r="I39" s="5"/>
       <c r="J39" s="4" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="K39" s="4"/>
       <c r="L39" s="5"/>
@@ -3525,7 +3557,7 @@
       <c r="O39" s="5"/>
     </row>
     <row r="40" s="1" customFormat="1" spans="1:15">
-      <c r="A40" s="21"/>
+      <c r="A40" s="22"/>
       <c r="B40" s="4" t="s">
         <v>54</v>
       </c>
@@ -3539,7 +3571,7 @@
       <c r="H40" s="5"/>
       <c r="I40" s="5"/>
       <c r="J40" s="4" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="K40" s="4"/>
       <c r="L40" s="5"/>
@@ -3548,15 +3580,15 @@
       <c r="O40" s="5"/>
     </row>
     <row r="41" s="1" customFormat="1" spans="1:15">
-      <c r="A41" s="21"/>
+      <c r="A41" s="22"/>
       <c r="B41" s="4" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="C41" s="4"/>
       <c r="D41" s="5"/>
       <c r="E41" s="5"/>
       <c r="F41" s="4" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="G41" s="9"/>
       <c r="H41" s="9"/>
@@ -3569,7 +3601,7 @@
       <c r="O41" s="5"/>
     </row>
     <row r="42" s="1" customFormat="1" spans="1:15">
-      <c r="A42" s="21"/>
+      <c r="A42" s="22"/>
       <c r="B42" s="4" t="s">
         <v>87</v>
       </c>
@@ -3590,42 +3622,42 @@
       <c r="O42" s="5"/>
     </row>
     <row r="43" s="1" customFormat="1" spans="1:15">
-      <c r="A43" s="21"/>
-      <c r="B43" s="22" t="s">
-        <v>129</v>
-      </c>
-      <c r="C43" s="22"/>
-      <c r="D43" s="22"/>
-      <c r="E43" s="22"/>
-      <c r="F43" s="22"/>
-      <c r="G43" s="22"/>
-      <c r="H43" s="22"/>
-      <c r="I43" s="22"/>
-      <c r="J43" s="37"/>
-      <c r="K43" s="38"/>
-      <c r="L43" s="37"/>
-      <c r="M43" s="46"/>
-      <c r="N43" s="46"/>
-      <c r="O43" s="38"/>
+      <c r="A43" s="22"/>
+      <c r="B43" s="23" t="s">
+        <v>130</v>
+      </c>
+      <c r="C43" s="23"/>
+      <c r="D43" s="23"/>
+      <c r="E43" s="23"/>
+      <c r="F43" s="23"/>
+      <c r="G43" s="23"/>
+      <c r="H43" s="23"/>
+      <c r="I43" s="23"/>
+      <c r="J43" s="40"/>
+      <c r="K43" s="41"/>
+      <c r="L43" s="40"/>
+      <c r="M43" s="50"/>
+      <c r="N43" s="50"/>
+      <c r="O43" s="41"/>
     </row>
     <row r="44" s="1" customFormat="1" spans="1:15">
-      <c r="A44" s="21"/>
+      <c r="A44" s="22"/>
       <c r="B44" s="4" t="s">
         <v>29</v>
       </c>
       <c r="C44" s="4" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="D44" s="4"/>
       <c r="E44" s="4" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="F44" s="4" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="G44" s="4"/>
       <c r="H44" s="4" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="I44" s="4"/>
       <c r="J44" s="4"/>
@@ -3636,7 +3668,7 @@
       <c r="O44" s="4"/>
     </row>
     <row r="45" s="1" customFormat="1" spans="1:15">
-      <c r="A45" s="21"/>
+      <c r="A45" s="22"/>
       <c r="B45" s="9">
         <v>1</v>
       </c>
@@ -3655,38 +3687,38 @@
       <c r="O45" s="9"/>
     </row>
     <row r="46" s="1" customFormat="1" spans="1:15">
-      <c r="A46" s="23"/>
+      <c r="A46" s="24"/>
       <c r="B46" s="9"/>
       <c r="C46" s="6"/>
-      <c r="D46" s="24"/>
+      <c r="D46" s="25"/>
       <c r="E46" s="5"/>
       <c r="F46" s="6"/>
-      <c r="G46" s="29"/>
+      <c r="G46" s="30"/>
       <c r="H46" s="6"/>
-      <c r="I46" s="29"/>
-      <c r="J46" s="39"/>
-      <c r="K46" s="40"/>
-      <c r="L46" s="39"/>
-      <c r="M46" s="47"/>
-      <c r="N46" s="47"/>
-      <c r="O46" s="40"/>
+      <c r="I46" s="30"/>
+      <c r="J46" s="42"/>
+      <c r="K46" s="43"/>
+      <c r="L46" s="42"/>
+      <c r="M46" s="51"/>
+      <c r="N46" s="51"/>
+      <c r="O46" s="43"/>
     </row>
     <row r="47" s="1" customFormat="1" spans="1:15">
-      <c r="A47" s="25"/>
+      <c r="A47" s="26"/>
       <c r="B47" s="9"/>
       <c r="C47" s="6"/>
-      <c r="D47" s="24"/>
+      <c r="D47" s="25"/>
       <c r="E47" s="5"/>
       <c r="F47" s="6"/>
-      <c r="G47" s="29"/>
+      <c r="G47" s="30"/>
       <c r="H47" s="6"/>
-      <c r="I47" s="29"/>
-      <c r="J47" s="39"/>
-      <c r="K47" s="40"/>
-      <c r="L47" s="39"/>
-      <c r="M47" s="47"/>
-      <c r="N47" s="47"/>
-      <c r="O47" s="40"/>
+      <c r="I47" s="30"/>
+      <c r="J47" s="42"/>
+      <c r="K47" s="43"/>
+      <c r="L47" s="42"/>
+      <c r="M47" s="51"/>
+      <c r="N47" s="51"/>
+      <c r="O47" s="43"/>
     </row>
   </sheetData>
   <mergeCells count="118">
@@ -3841,7 +3873,7 @@
       <c r="B1" s="4"/>
       <c r="C1" s="4"/>
       <c r="D1" s="5" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="E1" s="5"/>
       <c r="F1" s="5"/>
@@ -3849,15 +3881,15 @@
         <v>82</v>
       </c>
       <c r="H1" s="6" t="s">
-        <v>135</v>
-      </c>
-      <c r="I1" s="24"/>
-      <c r="J1" s="24"/>
-      <c r="K1" s="24"/>
-      <c r="L1" s="24"/>
-      <c r="M1" s="24"/>
-      <c r="N1" s="24"/>
-      <c r="O1" s="29"/>
+        <v>136</v>
+      </c>
+      <c r="I1" s="25"/>
+      <c r="J1" s="25"/>
+      <c r="K1" s="25"/>
+      <c r="L1" s="25"/>
+      <c r="M1" s="25"/>
+      <c r="N1" s="25"/>
+      <c r="O1" s="30"/>
     </row>
     <row r="2" s="1" customFormat="1" spans="1:15">
       <c r="A2" s="4" t="s">
@@ -3866,7 +3898,7 @@
       <c r="B2" s="4"/>
       <c r="C2" s="4"/>
       <c r="D2" s="5" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="E2" s="5"/>
       <c r="F2" s="5"/>
@@ -3874,13 +3906,13 @@
         <v>85</v>
       </c>
       <c r="H2" s="6"/>
-      <c r="I2" s="24"/>
-      <c r="J2" s="24"/>
-      <c r="K2" s="24"/>
-      <c r="L2" s="24"/>
-      <c r="M2" s="24"/>
-      <c r="N2" s="24"/>
-      <c r="O2" s="29"/>
+      <c r="I2" s="25"/>
+      <c r="J2" s="25"/>
+      <c r="K2" s="25"/>
+      <c r="L2" s="25"/>
+      <c r="M2" s="25"/>
+      <c r="N2" s="25"/>
+      <c r="O2" s="30"/>
     </row>
     <row r="3" s="1" customFormat="1" spans="1:15">
       <c r="A3" s="4" t="s">
@@ -3895,13 +3927,13 @@
         <v>86</v>
       </c>
       <c r="H3" s="6"/>
-      <c r="I3" s="24"/>
-      <c r="J3" s="24"/>
-      <c r="K3" s="24"/>
-      <c r="L3" s="24"/>
-      <c r="M3" s="24"/>
-      <c r="N3" s="24"/>
-      <c r="O3" s="29"/>
+      <c r="I3" s="25"/>
+      <c r="J3" s="25"/>
+      <c r="K3" s="25"/>
+      <c r="L3" s="25"/>
+      <c r="M3" s="25"/>
+      <c r="N3" s="25"/>
+      <c r="O3" s="30"/>
     </row>
     <row r="4" s="1" customFormat="1" spans="1:15">
       <c r="A4" s="4" t="s">
@@ -3910,19 +3942,19 @@
       <c r="B4" s="4"/>
       <c r="C4" s="4"/>
       <c r="D4" s="6" t="s">
-        <v>137</v>
-      </c>
-      <c r="E4" s="24"/>
-      <c r="F4" s="24"/>
-      <c r="G4" s="24"/>
-      <c r="H4" s="24"/>
-      <c r="I4" s="24"/>
-      <c r="J4" s="24"/>
-      <c r="K4" s="24"/>
-      <c r="L4" s="24"/>
-      <c r="M4" s="24"/>
-      <c r="N4" s="24"/>
-      <c r="O4" s="29"/>
+        <v>138</v>
+      </c>
+      <c r="E4" s="25"/>
+      <c r="F4" s="25"/>
+      <c r="G4" s="25"/>
+      <c r="H4" s="25"/>
+      <c r="I4" s="25"/>
+      <c r="J4" s="25"/>
+      <c r="K4" s="25"/>
+      <c r="L4" s="25"/>
+      <c r="M4" s="25"/>
+      <c r="N4" s="25"/>
+      <c r="O4" s="30"/>
     </row>
     <row r="5" s="1" customFormat="1" spans="1:15">
       <c r="A5" s="7"/>
@@ -4014,7 +4046,9 @@
       <c r="B8" s="9" t="s">
         <v>98</v>
       </c>
-      <c r="C8" s="9"/>
+      <c r="C8" s="9" t="s">
+        <v>99</v>
+      </c>
       <c r="D8" s="5" t="s">
         <v>100</v>
       </c>
@@ -4026,16 +4060,16 @@
       <c r="H8" s="9" t="s">
         <v>102</v>
       </c>
-      <c r="I8" s="30" t="s">
+      <c r="I8" s="31" t="s">
         <v>37</v>
       </c>
-      <c r="J8" s="31">
+      <c r="J8" s="32">
         <v>50</v>
       </c>
       <c r="K8" s="9"/>
-      <c r="L8" s="32"/>
+      <c r="L8" s="33"/>
       <c r="M8" s="5"/>
-      <c r="N8" s="32"/>
+      <c r="N8" s="33"/>
       <c r="O8" s="9"/>
     </row>
     <row r="9" s="2" customFormat="1" ht="15" spans="1:15">
@@ -4045,27 +4079,27 @@
       <c r="B9" s="9"/>
       <c r="C9" s="9"/>
       <c r="D9" s="5" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="E9" s="9"/>
       <c r="F9" s="5" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="G9" s="5"/>
       <c r="H9" s="9" t="s">
         <v>102</v>
       </c>
-      <c r="I9" s="30" t="s">
+      <c r="I9" s="31" t="s">
         <v>37</v>
       </c>
-      <c r="J9" s="31">
+      <c r="J9" s="32">
         <v>50</v>
       </c>
       <c r="K9" s="9"/>
-      <c r="L9" s="32"/>
+      <c r="L9" s="33"/>
       <c r="M9" s="5"/>
-      <c r="N9" s="33"/>
-      <c r="O9" s="41"/>
+      <c r="N9" s="34"/>
+      <c r="O9" s="44"/>
     </row>
     <row r="10" s="1" customFormat="1" ht="15" spans="1:15">
       <c r="A10" s="10">
@@ -4074,26 +4108,26 @@
       <c r="B10" s="10"/>
       <c r="C10" s="10"/>
       <c r="D10" s="5" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="E10" s="9"/>
       <c r="F10" s="5" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="G10" s="5"/>
       <c r="H10" s="9" t="s">
         <v>102</v>
       </c>
-      <c r="I10" s="30" t="s">
+      <c r="I10" s="31" t="s">
         <v>37</v>
       </c>
-      <c r="J10" s="31">
+      <c r="J10" s="32">
         <v>50</v>
       </c>
       <c r="K10" s="10"/>
-      <c r="L10" s="33"/>
-      <c r="M10" s="42"/>
-      <c r="N10" s="32"/>
+      <c r="L10" s="34"/>
+      <c r="M10" s="45"/>
+      <c r="N10" s="33"/>
       <c r="O10" s="9"/>
     </row>
     <row r="11" s="1" customFormat="1" ht="15" spans="1:15">
@@ -4103,30 +4137,30 @@
       <c r="B11" s="9"/>
       <c r="C11" s="9"/>
       <c r="D11" s="5" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="E11" s="9"/>
       <c r="F11" s="5" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="G11" s="5"/>
       <c r="H11" s="9" t="s">
         <v>102</v>
       </c>
-      <c r="I11" s="30" t="s">
+      <c r="I11" s="31" t="s">
         <v>37</v>
       </c>
-      <c r="J11" s="31">
+      <c r="J11" s="32">
         <v>100</v>
       </c>
       <c r="K11" s="9"/>
-      <c r="L11" s="32" t="s">
+      <c r="L11" s="33" t="s">
         <v>67</v>
       </c>
       <c r="M11" s="5" t="s">
         <v>61</v>
       </c>
-      <c r="N11" s="32"/>
+      <c r="N11" s="33"/>
       <c r="O11" s="9"/>
     </row>
     <row r="12" s="1" customFormat="1" ht="15" spans="1:15">
@@ -4138,12 +4172,12 @@
       <c r="F12" s="5"/>
       <c r="G12" s="5"/>
       <c r="H12" s="9"/>
-      <c r="I12" s="30"/>
-      <c r="J12" s="31"/>
+      <c r="I12" s="31"/>
+      <c r="J12" s="32"/>
       <c r="K12" s="9"/>
-      <c r="L12" s="32"/>
+      <c r="L12" s="33"/>
       <c r="M12" s="5"/>
-      <c r="N12" s="32"/>
+      <c r="N12" s="33"/>
       <c r="O12" s="9"/>
     </row>
     <row r="13" s="1" customFormat="1" ht="15" spans="1:15">
@@ -4155,12 +4189,12 @@
       <c r="F13" s="5"/>
       <c r="G13" s="5"/>
       <c r="H13" s="9"/>
-      <c r="I13" s="30"/>
-      <c r="J13" s="31"/>
+      <c r="I13" s="31"/>
+      <c r="J13" s="32"/>
       <c r="K13" s="9"/>
-      <c r="L13" s="32"/>
+      <c r="L13" s="33"/>
       <c r="M13" s="5"/>
-      <c r="N13" s="32"/>
+      <c r="N13" s="33"/>
       <c r="O13" s="9"/>
     </row>
     <row r="14" s="1" customFormat="1" ht="15" spans="1:15">
@@ -4172,12 +4206,12 @@
       <c r="F14" s="5"/>
       <c r="G14" s="5"/>
       <c r="H14" s="9"/>
-      <c r="I14" s="30"/>
-      <c r="J14" s="31"/>
+      <c r="I14" s="31"/>
+      <c r="J14" s="32"/>
       <c r="K14" s="9"/>
-      <c r="L14" s="32"/>
+      <c r="L14" s="33"/>
       <c r="M14" s="5"/>
-      <c r="N14" s="32"/>
+      <c r="N14" s="33"/>
       <c r="O14" s="9"/>
     </row>
     <row r="15" s="1" customFormat="1" ht="15" spans="1:15">
@@ -4189,12 +4223,12 @@
       <c r="F15" s="5"/>
       <c r="G15" s="5"/>
       <c r="H15" s="9"/>
-      <c r="I15" s="34"/>
-      <c r="J15" s="31"/>
+      <c r="I15" s="35"/>
+      <c r="J15" s="32"/>
       <c r="K15" s="9"/>
-      <c r="L15" s="32"/>
+      <c r="L15" s="33"/>
       <c r="M15" s="5"/>
-      <c r="N15" s="32"/>
+      <c r="N15" s="33"/>
       <c r="O15" s="9"/>
     </row>
     <row r="16" s="1" customFormat="1" ht="15" spans="1:15">
@@ -4206,12 +4240,12 @@
       <c r="F16" s="5"/>
       <c r="G16" s="5"/>
       <c r="H16" s="9"/>
-      <c r="I16" s="34"/>
-      <c r="J16" s="31"/>
+      <c r="I16" s="35"/>
+      <c r="J16" s="32"/>
       <c r="K16" s="9"/>
-      <c r="L16" s="32"/>
+      <c r="L16" s="33"/>
       <c r="M16" s="5"/>
-      <c r="N16" s="32"/>
+      <c r="N16" s="33"/>
       <c r="O16" s="9"/>
     </row>
     <row r="17" s="1" customFormat="1" ht="15" spans="1:15">
@@ -4223,12 +4257,12 @@
       <c r="F17" s="5"/>
       <c r="G17" s="5"/>
       <c r="H17" s="9"/>
-      <c r="I17" s="34"/>
-      <c r="J17" s="31"/>
+      <c r="I17" s="35"/>
+      <c r="J17" s="32"/>
       <c r="K17" s="9"/>
-      <c r="L17" s="32"/>
+      <c r="L17" s="33"/>
       <c r="M17" s="5"/>
-      <c r="N17" s="32"/>
+      <c r="N17" s="33"/>
       <c r="O17" s="9"/>
     </row>
     <row r="18" s="1" customFormat="1" ht="15" spans="1:15">
@@ -4240,12 +4274,12 @@
       <c r="F18" s="5"/>
       <c r="G18" s="5"/>
       <c r="H18" s="9"/>
-      <c r="I18" s="34"/>
-      <c r="J18" s="31"/>
+      <c r="I18" s="35"/>
+      <c r="J18" s="32"/>
       <c r="K18" s="9"/>
-      <c r="L18" s="32"/>
+      <c r="L18" s="33"/>
       <c r="M18" s="5"/>
-      <c r="N18" s="32"/>
+      <c r="N18" s="33"/>
       <c r="O18" s="9"/>
     </row>
     <row r="19" s="1" customFormat="1" ht="15" spans="1:15">
@@ -4257,12 +4291,12 @@
       <c r="F19" s="5"/>
       <c r="G19" s="5"/>
       <c r="H19" s="9"/>
-      <c r="I19" s="34"/>
-      <c r="J19" s="31"/>
+      <c r="I19" s="35"/>
+      <c r="J19" s="32"/>
       <c r="K19" s="9"/>
-      <c r="L19" s="32"/>
+      <c r="L19" s="33"/>
       <c r="M19" s="5"/>
-      <c r="N19" s="32"/>
+      <c r="N19" s="33"/>
       <c r="O19" s="9"/>
     </row>
     <row r="20" s="1" customFormat="1" spans="1:15">
@@ -4277,9 +4311,9 @@
       <c r="I20" s="9"/>
       <c r="J20" s="9"/>
       <c r="K20" s="9"/>
-      <c r="L20" s="32"/>
+      <c r="L20" s="33"/>
       <c r="M20" s="5"/>
-      <c r="N20" s="32"/>
+      <c r="N20" s="33"/>
       <c r="O20" s="9"/>
     </row>
     <row r="21" s="3" customFormat="1" spans="1:15">
@@ -4297,11 +4331,11 @@
       <c r="L21" s="12"/>
       <c r="M21" s="12"/>
       <c r="N21" s="12"/>
-      <c r="O21" s="43"/>
+      <c r="O21" s="46"/>
     </row>
     <row r="22" s="3" customFormat="1" spans="1:15">
       <c r="A22" s="13" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="B22" s="14"/>
       <c r="C22" s="14"/>
@@ -4316,14 +4350,14 @@
       <c r="L22" s="14"/>
       <c r="M22" s="14"/>
       <c r="N22" s="14"/>
-      <c r="O22" s="44"/>
+      <c r="O22" s="47"/>
     </row>
     <row r="23" s="3" customFormat="1" spans="1:15">
       <c r="A23" s="15" t="s">
         <v>29</v>
       </c>
       <c r="B23" s="16" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="C23" s="17"/>
       <c r="D23" s="16" t="s">
@@ -4336,107 +4370,115 @@
         <v>56</v>
       </c>
       <c r="G23" s="15" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="H23" s="15"/>
       <c r="I23" s="15"/>
       <c r="J23" s="16" t="s">
-        <v>121</v>
-      </c>
-      <c r="K23" s="35"/>
-      <c r="L23" s="35"/>
-      <c r="M23" s="35"/>
-      <c r="N23" s="35"/>
+        <v>122</v>
+      </c>
+      <c r="K23" s="36"/>
+      <c r="L23" s="36"/>
+      <c r="M23" s="36"/>
+      <c r="N23" s="36"/>
       <c r="O23" s="17"/>
     </row>
-    <row r="24" s="3" customFormat="1" spans="1:15">
-      <c r="A24" s="18"/>
-      <c r="B24" s="18"/>
-      <c r="C24" s="18"/>
-      <c r="D24" s="18"/>
-      <c r="E24" s="26"/>
-      <c r="F24" s="26"/>
-      <c r="G24" s="27"/>
-      <c r="H24" s="28"/>
-      <c r="I24" s="36"/>
-      <c r="J24" s="27"/>
-      <c r="K24" s="28"/>
-      <c r="L24" s="28"/>
-      <c r="M24" s="28"/>
-      <c r="N24" s="28"/>
-      <c r="O24" s="36"/>
+    <row r="24" s="3" customFormat="1" ht="45" customHeight="1" spans="1:15">
+      <c r="A24" s="18">
+        <v>1</v>
+      </c>
+      <c r="B24" s="19" t="s">
+        <v>145</v>
+      </c>
+      <c r="C24" s="19"/>
+      <c r="D24" s="18" t="s">
+        <v>146</v>
+      </c>
+      <c r="E24" s="27"/>
+      <c r="F24" s="27"/>
+      <c r="G24" s="28" t="s">
+        <v>145</v>
+      </c>
+      <c r="H24" s="29"/>
+      <c r="I24" s="37"/>
+      <c r="J24" s="38"/>
+      <c r="K24" s="39"/>
+      <c r="L24" s="39"/>
+      <c r="M24" s="39"/>
+      <c r="N24" s="39"/>
+      <c r="O24" s="48"/>
     </row>
     <row r="25" s="3" customFormat="1" spans="1:15">
       <c r="A25" s="18"/>
-      <c r="B25" s="18"/>
-      <c r="C25" s="18"/>
+      <c r="B25" s="19"/>
+      <c r="C25" s="19"/>
       <c r="D25" s="18"/>
-      <c r="E25" s="26"/>
-      <c r="F25" s="26"/>
-      <c r="G25" s="27"/>
-      <c r="H25" s="28"/>
-      <c r="I25" s="36"/>
-      <c r="J25" s="27"/>
-      <c r="K25" s="28"/>
-      <c r="L25" s="28"/>
-      <c r="M25" s="28"/>
-      <c r="N25" s="28"/>
-      <c r="O25" s="36"/>
+      <c r="E25" s="27"/>
+      <c r="F25" s="27"/>
+      <c r="G25" s="28"/>
+      <c r="H25" s="29"/>
+      <c r="I25" s="37"/>
+      <c r="J25" s="38"/>
+      <c r="K25" s="39"/>
+      <c r="L25" s="39"/>
+      <c r="M25" s="39"/>
+      <c r="N25" s="39"/>
+      <c r="O25" s="48"/>
     </row>
     <row r="26" s="3" customFormat="1" spans="1:15">
       <c r="A26" s="18"/>
-      <c r="B26" s="18"/>
-      <c r="C26" s="18"/>
+      <c r="B26" s="19"/>
+      <c r="C26" s="19"/>
       <c r="D26" s="18"/>
-      <c r="E26" s="26"/>
-      <c r="F26" s="26"/>
-      <c r="G26" s="27"/>
-      <c r="H26" s="28"/>
-      <c r="I26" s="36"/>
-      <c r="J26" s="27"/>
-      <c r="K26" s="28"/>
-      <c r="L26" s="28"/>
-      <c r="M26" s="28"/>
-      <c r="N26" s="28"/>
-      <c r="O26" s="36"/>
+      <c r="E26" s="27"/>
+      <c r="F26" s="27"/>
+      <c r="G26" s="28"/>
+      <c r="H26" s="29"/>
+      <c r="I26" s="37"/>
+      <c r="J26" s="38"/>
+      <c r="K26" s="39"/>
+      <c r="L26" s="39"/>
+      <c r="M26" s="39"/>
+      <c r="N26" s="39"/>
+      <c r="O26" s="48"/>
     </row>
     <row r="27" s="3" customFormat="1" spans="1:15">
       <c r="A27" s="18"/>
-      <c r="B27" s="18"/>
-      <c r="C27" s="18"/>
+      <c r="B27" s="19"/>
+      <c r="C27" s="19"/>
       <c r="D27" s="18"/>
-      <c r="E27" s="26"/>
-      <c r="F27" s="26"/>
-      <c r="G27" s="27"/>
-      <c r="H27" s="28"/>
-      <c r="I27" s="36"/>
-      <c r="J27" s="27"/>
-      <c r="K27" s="28"/>
-      <c r="L27" s="28"/>
-      <c r="M27" s="28"/>
-      <c r="N27" s="28"/>
-      <c r="O27" s="36"/>
+      <c r="E27" s="27"/>
+      <c r="F27" s="27"/>
+      <c r="G27" s="28"/>
+      <c r="H27" s="29"/>
+      <c r="I27" s="37"/>
+      <c r="J27" s="38"/>
+      <c r="K27" s="39"/>
+      <c r="L27" s="39"/>
+      <c r="M27" s="39"/>
+      <c r="N27" s="39"/>
+      <c r="O27" s="48"/>
     </row>
     <row r="28" s="1" customFormat="1" spans="1:15">
-      <c r="A28" s="19"/>
-      <c r="B28" s="20"/>
-      <c r="C28" s="20"/>
-      <c r="D28" s="20"/>
-      <c r="E28" s="20"/>
-      <c r="F28" s="20"/>
-      <c r="G28" s="20"/>
-      <c r="H28" s="20"/>
-      <c r="I28" s="20"/>
-      <c r="J28" s="20"/>
-      <c r="K28" s="20"/>
-      <c r="L28" s="20"/>
-      <c r="M28" s="20"/>
-      <c r="N28" s="20"/>
-      <c r="O28" s="45"/>
+      <c r="A28" s="20"/>
+      <c r="B28" s="21"/>
+      <c r="C28" s="21"/>
+      <c r="D28" s="21"/>
+      <c r="E28" s="21"/>
+      <c r="F28" s="21"/>
+      <c r="G28" s="21"/>
+      <c r="H28" s="21"/>
+      <c r="I28" s="21"/>
+      <c r="J28" s="21"/>
+      <c r="K28" s="21"/>
+      <c r="L28" s="21"/>
+      <c r="M28" s="21"/>
+      <c r="N28" s="21"/>
+      <c r="O28" s="49"/>
     </row>
     <row r="29" s="1" customFormat="1" spans="1:15">
       <c r="A29" s="8" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="B29" s="8"/>
       <c r="C29" s="8"/>
@@ -4454,25 +4496,27 @@
       <c r="O29" s="8"/>
     </row>
     <row r="30" s="1" customFormat="1" spans="1:15">
-      <c r="A30" s="21">
+      <c r="A30" s="22">
         <v>1</v>
       </c>
       <c r="B30" s="4" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="C30" s="4"/>
       <c r="D30" s="5" t="s">
-        <v>144</v>
+        <v>147</v>
       </c>
       <c r="E30" s="5"/>
       <c r="F30" s="4" t="s">
-        <v>124</v>
-      </c>
-      <c r="G30" s="5"/>
+        <v>125</v>
+      </c>
+      <c r="G30" s="5" t="s">
+        <v>148</v>
+      </c>
       <c r="H30" s="5"/>
       <c r="I30" s="5"/>
       <c r="J30" s="4" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="K30" s="4"/>
       <c r="L30" s="5" t="s">
@@ -4483,7 +4527,7 @@
       <c r="O30" s="5"/>
     </row>
     <row r="31" s="1" customFormat="1" spans="1:15">
-      <c r="A31" s="21"/>
+      <c r="A31" s="22"/>
       <c r="B31" s="4" t="s">
         <v>54</v>
       </c>
@@ -4497,26 +4541,26 @@
       <c r="H31" s="5"/>
       <c r="I31" s="5"/>
       <c r="J31" s="4" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="K31" s="4"/>
       <c r="L31" s="5" t="s">
-        <v>145</v>
+        <v>149</v>
       </c>
       <c r="M31" s="5"/>
       <c r="N31" s="5"/>
       <c r="O31" s="5"/>
     </row>
     <row r="32" s="1" customFormat="1" spans="1:15">
-      <c r="A32" s="21"/>
+      <c r="A32" s="22"/>
       <c r="B32" s="4" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="C32" s="4"/>
       <c r="D32" s="5"/>
       <c r="E32" s="5"/>
       <c r="F32" s="4" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="G32" s="9"/>
       <c r="H32" s="9"/>
@@ -4529,7 +4573,7 @@
       <c r="O32" s="5"/>
     </row>
     <row r="33" s="1" customFormat="1" spans="1:15">
-      <c r="A33" s="21"/>
+      <c r="A33" s="22"/>
       <c r="B33" s="4" t="s">
         <v>87</v>
       </c>
@@ -4545,49 +4589,49 @@
       </c>
       <c r="K33" s="4"/>
       <c r="L33" s="5" t="s">
-        <v>146</v>
+        <v>150</v>
       </c>
       <c r="M33" s="5"/>
       <c r="N33" s="5"/>
       <c r="O33" s="5"/>
     </row>
     <row r="34" s="1" customFormat="1" spans="1:15">
-      <c r="A34" s="21"/>
-      <c r="B34" s="22" t="s">
-        <v>129</v>
-      </c>
-      <c r="C34" s="22"/>
-      <c r="D34" s="22"/>
-      <c r="E34" s="22"/>
-      <c r="F34" s="22"/>
-      <c r="G34" s="22"/>
-      <c r="H34" s="22"/>
-      <c r="I34" s="22"/>
-      <c r="J34" s="37"/>
-      <c r="K34" s="38"/>
-      <c r="L34" s="37"/>
-      <c r="M34" s="46"/>
-      <c r="N34" s="46"/>
-      <c r="O34" s="38"/>
+      <c r="A34" s="22"/>
+      <c r="B34" s="23" t="s">
+        <v>130</v>
+      </c>
+      <c r="C34" s="23"/>
+      <c r="D34" s="23"/>
+      <c r="E34" s="23"/>
+      <c r="F34" s="23"/>
+      <c r="G34" s="23"/>
+      <c r="H34" s="23"/>
+      <c r="I34" s="23"/>
+      <c r="J34" s="40"/>
+      <c r="K34" s="41"/>
+      <c r="L34" s="40"/>
+      <c r="M34" s="50"/>
+      <c r="N34" s="50"/>
+      <c r="O34" s="41"/>
     </row>
     <row r="35" s="1" customFormat="1" spans="1:15">
-      <c r="A35" s="21"/>
+      <c r="A35" s="22"/>
       <c r="B35" s="4" t="s">
         <v>29</v>
       </c>
       <c r="C35" s="4" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="D35" s="4"/>
       <c r="E35" s="4" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="F35" s="4" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="G35" s="4"/>
       <c r="H35" s="4" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="I35" s="4"/>
       <c r="J35" s="4"/>
@@ -4598,12 +4642,12 @@
       <c r="O35" s="4"/>
     </row>
     <row r="36" s="1" customFormat="1" spans="1:15">
-      <c r="A36" s="21"/>
+      <c r="A36" s="22"/>
       <c r="B36" s="9">
         <v>1</v>
       </c>
       <c r="C36" s="5" t="s">
-        <v>147</v>
+        <v>151</v>
       </c>
       <c r="D36" s="5"/>
       <c r="E36" s="5"/>
@@ -4621,59 +4665,61 @@
       <c r="O36" s="9"/>
     </row>
     <row r="37" s="1" customFormat="1" spans="1:15">
-      <c r="A37" s="23"/>
+      <c r="A37" s="24"/>
       <c r="B37" s="9"/>
       <c r="C37" s="6"/>
-      <c r="D37" s="24"/>
+      <c r="D37" s="25"/>
       <c r="E37" s="5"/>
       <c r="F37" s="6"/>
-      <c r="G37" s="29"/>
+      <c r="G37" s="30"/>
       <c r="H37" s="6"/>
-      <c r="I37" s="29"/>
-      <c r="J37" s="39"/>
-      <c r="K37" s="40"/>
-      <c r="L37" s="39"/>
-      <c r="M37" s="47"/>
-      <c r="N37" s="47"/>
-      <c r="O37" s="40"/>
+      <c r="I37" s="30"/>
+      <c r="J37" s="42"/>
+      <c r="K37" s="43"/>
+      <c r="L37" s="42"/>
+      <c r="M37" s="51"/>
+      <c r="N37" s="51"/>
+      <c r="O37" s="43"/>
     </row>
     <row r="38" s="1" customFormat="1" spans="1:15">
-      <c r="A38" s="25"/>
+      <c r="A38" s="26"/>
       <c r="B38" s="9"/>
       <c r="C38" s="6"/>
-      <c r="D38" s="24"/>
+      <c r="D38" s="25"/>
       <c r="E38" s="5"/>
       <c r="F38" s="6"/>
-      <c r="G38" s="29"/>
+      <c r="G38" s="30"/>
       <c r="H38" s="6"/>
-      <c r="I38" s="29"/>
-      <c r="J38" s="39"/>
-      <c r="K38" s="40"/>
-      <c r="L38" s="39"/>
-      <c r="M38" s="47"/>
-      <c r="N38" s="47"/>
-      <c r="O38" s="40"/>
+      <c r="I38" s="30"/>
+      <c r="J38" s="42"/>
+      <c r="K38" s="43"/>
+      <c r="L38" s="42"/>
+      <c r="M38" s="51"/>
+      <c r="N38" s="51"/>
+      <c r="O38" s="43"/>
     </row>
     <row r="39" s="1" customFormat="1" spans="1:15">
-      <c r="A39" s="21">
+      <c r="A39" s="22">
         <v>2</v>
       </c>
       <c r="B39" s="4" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="C39" s="4"/>
       <c r="D39" s="5" t="s">
-        <v>148</v>
+        <v>152</v>
       </c>
       <c r="E39" s="5"/>
       <c r="F39" s="4" t="s">
-        <v>124</v>
-      </c>
-      <c r="G39" s="5"/>
+        <v>125</v>
+      </c>
+      <c r="G39" s="5" t="s">
+        <v>153</v>
+      </c>
       <c r="H39" s="5"/>
       <c r="I39" s="5"/>
       <c r="J39" s="4" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="K39" s="4"/>
       <c r="L39" s="5" t="s">
@@ -4684,7 +4730,7 @@
       <c r="O39" s="5"/>
     </row>
     <row r="40" s="1" customFormat="1" spans="1:15">
-      <c r="A40" s="21"/>
+      <c r="A40" s="22"/>
       <c r="B40" s="4" t="s">
         <v>54</v>
       </c>
@@ -4698,26 +4744,26 @@
       <c r="H40" s="5"/>
       <c r="I40" s="5"/>
       <c r="J40" s="4" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="K40" s="4"/>
       <c r="L40" s="5" t="s">
-        <v>145</v>
+        <v>149</v>
       </c>
       <c r="M40" s="5"/>
       <c r="N40" s="5"/>
       <c r="O40" s="5"/>
     </row>
     <row r="41" s="1" customFormat="1" spans="1:15">
-      <c r="A41" s="21"/>
+      <c r="A41" s="22"/>
       <c r="B41" s="4" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="C41" s="4"/>
       <c r="D41" s="5"/>
       <c r="E41" s="5"/>
       <c r="F41" s="4" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="G41" s="9"/>
       <c r="H41" s="9"/>
@@ -4730,7 +4776,7 @@
       <c r="O41" s="5"/>
     </row>
     <row r="42" s="1" customFormat="1" spans="1:15">
-      <c r="A42" s="21"/>
+      <c r="A42" s="22"/>
       <c r="B42" s="4" t="s">
         <v>87</v>
       </c>
@@ -4746,49 +4792,49 @@
       </c>
       <c r="K42" s="4"/>
       <c r="L42" s="5" t="s">
-        <v>146</v>
+        <v>150</v>
       </c>
       <c r="M42" s="5"/>
       <c r="N42" s="5"/>
       <c r="O42" s="5"/>
     </row>
     <row r="43" s="1" customFormat="1" spans="1:15">
-      <c r="A43" s="21"/>
-      <c r="B43" s="22" t="s">
-        <v>129</v>
-      </c>
-      <c r="C43" s="22"/>
-      <c r="D43" s="22"/>
-      <c r="E43" s="22"/>
-      <c r="F43" s="22"/>
-      <c r="G43" s="22"/>
-      <c r="H43" s="22"/>
-      <c r="I43" s="22"/>
-      <c r="J43" s="37"/>
-      <c r="K43" s="38"/>
-      <c r="L43" s="37"/>
-      <c r="M43" s="46"/>
-      <c r="N43" s="46"/>
-      <c r="O43" s="38"/>
+      <c r="A43" s="22"/>
+      <c r="B43" s="23" t="s">
+        <v>130</v>
+      </c>
+      <c r="C43" s="23"/>
+      <c r="D43" s="23"/>
+      <c r="E43" s="23"/>
+      <c r="F43" s="23"/>
+      <c r="G43" s="23"/>
+      <c r="H43" s="23"/>
+      <c r="I43" s="23"/>
+      <c r="J43" s="40"/>
+      <c r="K43" s="41"/>
+      <c r="L43" s="40"/>
+      <c r="M43" s="50"/>
+      <c r="N43" s="50"/>
+      <c r="O43" s="41"/>
     </row>
     <row r="44" s="1" customFormat="1" spans="1:15">
-      <c r="A44" s="21"/>
+      <c r="A44" s="22"/>
       <c r="B44" s="4" t="s">
         <v>29</v>
       </c>
       <c r="C44" s="4" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="D44" s="4"/>
       <c r="E44" s="4" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="F44" s="4" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="G44" s="4"/>
       <c r="H44" s="4" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="I44" s="4"/>
       <c r="J44" s="4"/>
@@ -4799,12 +4845,12 @@
       <c r="O44" s="4"/>
     </row>
     <row r="45" s="1" customFormat="1" spans="1:15">
-      <c r="A45" s="21"/>
+      <c r="A45" s="22"/>
       <c r="B45" s="9">
         <v>1</v>
       </c>
       <c r="C45" s="5" t="s">
-        <v>149</v>
+        <v>154</v>
       </c>
       <c r="D45" s="5"/>
       <c r="E45" s="5"/>
@@ -4822,38 +4868,38 @@
       <c r="O45" s="9"/>
     </row>
     <row r="46" s="1" customFormat="1" spans="1:15">
-      <c r="A46" s="23"/>
+      <c r="A46" s="24"/>
       <c r="B46" s="9"/>
       <c r="C46" s="6"/>
-      <c r="D46" s="24"/>
+      <c r="D46" s="25"/>
       <c r="E46" s="5"/>
       <c r="F46" s="6"/>
-      <c r="G46" s="29"/>
+      <c r="G46" s="30"/>
       <c r="H46" s="6"/>
-      <c r="I46" s="29"/>
-      <c r="J46" s="39"/>
-      <c r="K46" s="40"/>
-      <c r="L46" s="39"/>
-      <c r="M46" s="47"/>
-      <c r="N46" s="47"/>
-      <c r="O46" s="40"/>
+      <c r="I46" s="30"/>
+      <c r="J46" s="42"/>
+      <c r="K46" s="43"/>
+      <c r="L46" s="42"/>
+      <c r="M46" s="51"/>
+      <c r="N46" s="51"/>
+      <c r="O46" s="43"/>
     </row>
     <row r="47" s="1" customFormat="1" spans="1:15">
-      <c r="A47" s="25"/>
+      <c r="A47" s="26"/>
       <c r="B47" s="9"/>
       <c r="C47" s="6"/>
-      <c r="D47" s="24"/>
+      <c r="D47" s="25"/>
       <c r="E47" s="5"/>
       <c r="F47" s="6"/>
-      <c r="G47" s="29"/>
+      <c r="G47" s="30"/>
       <c r="H47" s="6"/>
-      <c r="I47" s="29"/>
-      <c r="J47" s="39"/>
-      <c r="K47" s="40"/>
-      <c r="L47" s="39"/>
-      <c r="M47" s="47"/>
-      <c r="N47" s="47"/>
-      <c r="O47" s="40"/>
+      <c r="I47" s="30"/>
+      <c r="J47" s="42"/>
+      <c r="K47" s="43"/>
+      <c r="L47" s="42"/>
+      <c r="M47" s="51"/>
+      <c r="N47" s="51"/>
+      <c r="O47" s="43"/>
     </row>
   </sheetData>
   <mergeCells count="118">

--- a/600.store/model.orm.xlsx
+++ b/600.store/model.orm.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="317" uniqueCount="155">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="319" uniqueCount="157">
   <si>
     <t>#变量名</t>
   </si>
@@ -464,7 +464,10 @@
     <t>source</t>
   </si>
   <si>
-    <t>relationToList</t>
+    <t>relationships</t>
+  </si>
+  <si>
+    <t>人际关系</t>
   </si>
   <si>
     <t>to-one</t>
@@ -479,7 +482,10 @@
     <t>target</t>
   </si>
   <si>
-    <t>relationFromList</t>
+    <t>inverseRelationships</t>
+  </si>
+  <si>
+    <t>反向人际关系</t>
   </si>
   <si>
     <t>targetId</t>
@@ -4532,7 +4538,9 @@
         <v>54</v>
       </c>
       <c r="C31" s="4"/>
-      <c r="D31" s="5"/>
+      <c r="D31" s="5" t="s">
+        <v>149</v>
+      </c>
       <c r="E31" s="5"/>
       <c r="F31" s="4" t="s">
         <v>56</v>
@@ -4545,7 +4553,7 @@
       </c>
       <c r="K31" s="4"/>
       <c r="L31" s="5" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="M31" s="5"/>
       <c r="N31" s="5"/>
@@ -4589,7 +4597,7 @@
       </c>
       <c r="K33" s="4"/>
       <c r="L33" s="5" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="M33" s="5"/>
       <c r="N33" s="5"/>
@@ -4647,7 +4655,7 @@
         <v>1</v>
       </c>
       <c r="C36" s="5" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="D36" s="5"/>
       <c r="E36" s="5"/>
@@ -4707,14 +4715,14 @@
       </c>
       <c r="C39" s="4"/>
       <c r="D39" s="5" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="E39" s="5"/>
       <c r="F39" s="4" t="s">
         <v>125</v>
       </c>
       <c r="G39" s="5" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="H39" s="5"/>
       <c r="I39" s="5"/>
@@ -4735,7 +4743,9 @@
         <v>54</v>
       </c>
       <c r="C40" s="4"/>
-      <c r="D40" s="5"/>
+      <c r="D40" s="5" t="s">
+        <v>155</v>
+      </c>
       <c r="E40" s="5"/>
       <c r="F40" s="4" t="s">
         <v>56</v>
@@ -4748,7 +4758,7 @@
       </c>
       <c r="K40" s="4"/>
       <c r="L40" s="5" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="M40" s="5"/>
       <c r="N40" s="5"/>
@@ -4792,7 +4802,7 @@
       </c>
       <c r="K42" s="4"/>
       <c r="L42" s="5" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="M42" s="5"/>
       <c r="N42" s="5"/>
@@ -4850,7 +4860,7 @@
         <v>1</v>
       </c>
       <c r="C45" s="5" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="D45" s="5"/>
       <c r="E45" s="5"/>

--- a/600.store/model.orm.xlsx
+++ b/600.store/model.orm.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="12555" activeTab="4"/>
+    <workbookView windowWidth="28800" windowHeight="12555" activeTab="3"/>
   </bookViews>
   <sheets>
     <sheet name="配置" sheetId="2" r:id="rId1"/>
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="319" uniqueCount="157">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="314" uniqueCount="154">
   <si>
     <t>#变量名</t>
   </si>
@@ -357,15 +357,6 @@
   </si>
   <si>
     <t>身份证号</t>
-  </si>
-  <si>
-    <t>myself</t>
-  </si>
-  <si>
-    <t>「我」？</t>
-  </si>
-  <si>
-    <t>是否为资产库所有者。有且仅有一个</t>
   </si>
   <si>
     <t>deleted</t>
@@ -2672,7 +2663,7 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:O47"/>
+  <dimension ref="A1:O46"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="3" width="9" style="1"/>
@@ -3036,9 +3027,9 @@
       <c r="N13" s="33"/>
       <c r="O13" s="9"/>
     </row>
-    <row r="14" s="1" customFormat="1" ht="40.5" spans="1:15">
+    <row r="14" s="1" customFormat="1" ht="15" spans="1:15">
       <c r="A14" s="9">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B14" s="9"/>
       <c r="C14" s="9"/>
@@ -3049,11 +3040,13 @@
       <c r="F14" s="5" t="s">
         <v>114</v>
       </c>
-      <c r="G14" s="5"/>
+      <c r="G14" s="5" t="s">
+        <v>44</v>
+      </c>
       <c r="H14" s="9" t="s">
         <v>102</v>
       </c>
-      <c r="I14" s="31" t="s">
+      <c r="I14" s="35" t="s">
         <v>46</v>
       </c>
       <c r="J14" s="32"/>
@@ -3066,34 +3059,20 @@
       <c r="O14" s="9"/>
     </row>
     <row r="15" s="1" customFormat="1" ht="15" spans="1:15">
-      <c r="A15" s="9">
-        <v>8</v>
-      </c>
+      <c r="A15" s="9"/>
       <c r="B15" s="9"/>
       <c r="C15" s="9"/>
-      <c r="D15" s="5" t="s">
-        <v>116</v>
-      </c>
+      <c r="D15" s="5"/>
       <c r="E15" s="9"/>
-      <c r="F15" s="5" t="s">
-        <v>117</v>
-      </c>
-      <c r="G15" s="5" t="s">
-        <v>44</v>
-      </c>
-      <c r="H15" s="9" t="s">
-        <v>102</v>
-      </c>
-      <c r="I15" s="35" t="s">
-        <v>46</v>
-      </c>
+      <c r="F15" s="5"/>
+      <c r="G15" s="5"/>
+      <c r="H15" s="9"/>
+      <c r="I15" s="35"/>
       <c r="J15" s="32"/>
       <c r="K15" s="9"/>
       <c r="L15" s="33"/>
       <c r="M15" s="5"/>
-      <c r="N15" s="33" t="s">
-        <v>118</v>
-      </c>
+      <c r="N15" s="33"/>
       <c r="O15" s="9"/>
     </row>
     <row r="16" s="1" customFormat="1" ht="15" spans="1:15">
@@ -3147,106 +3126,106 @@
       <c r="N18" s="33"/>
       <c r="O18" s="9"/>
     </row>
-    <row r="19" s="1" customFormat="1" ht="15" spans="1:15">
+    <row r="19" s="1" customFormat="1" spans="1:15">
       <c r="A19" s="9"/>
       <c r="B19" s="9"/>
       <c r="C19" s="9"/>
-      <c r="D19" s="5"/>
+      <c r="D19" s="9"/>
       <c r="E19" s="9"/>
-      <c r="F19" s="5"/>
-      <c r="G19" s="5"/>
+      <c r="F19" s="9"/>
+      <c r="G19" s="9"/>
       <c r="H19" s="9"/>
-      <c r="I19" s="35"/>
-      <c r="J19" s="32"/>
+      <c r="I19" s="9"/>
+      <c r="J19" s="9"/>
       <c r="K19" s="9"/>
       <c r="L19" s="33"/>
       <c r="M19" s="5"/>
       <c r="N19" s="33"/>
       <c r="O19" s="9"/>
     </row>
-    <row r="20" s="1" customFormat="1" spans="1:15">
-      <c r="A20" s="9"/>
-      <c r="B20" s="9"/>
-      <c r="C20" s="9"/>
-      <c r="D20" s="9"/>
-      <c r="E20" s="9"/>
-      <c r="F20" s="9"/>
-      <c r="G20" s="9"/>
-      <c r="H20" s="9"/>
-      <c r="I20" s="9"/>
-      <c r="J20" s="9"/>
-      <c r="K20" s="9"/>
-      <c r="L20" s="33"/>
-      <c r="M20" s="5"/>
-      <c r="N20" s="33"/>
-      <c r="O20" s="9"/>
+    <row r="20" s="3" customFormat="1" spans="1:15">
+      <c r="A20" s="11"/>
+      <c r="B20" s="12"/>
+      <c r="C20" s="12"/>
+      <c r="D20" s="12"/>
+      <c r="E20" s="12"/>
+      <c r="F20" s="12"/>
+      <c r="G20" s="12"/>
+      <c r="H20" s="12"/>
+      <c r="I20" s="12"/>
+      <c r="J20" s="12"/>
+      <c r="K20" s="12"/>
+      <c r="L20" s="12"/>
+      <c r="M20" s="12"/>
+      <c r="N20" s="12"/>
+      <c r="O20" s="46"/>
     </row>
     <row r="21" s="3" customFormat="1" spans="1:15">
-      <c r="A21" s="11"/>
-      <c r="B21" s="12"/>
-      <c r="C21" s="12"/>
-      <c r="D21" s="12"/>
-      <c r="E21" s="12"/>
-      <c r="F21" s="12"/>
-      <c r="G21" s="12"/>
-      <c r="H21" s="12"/>
-      <c r="I21" s="12"/>
-      <c r="J21" s="12"/>
-      <c r="K21" s="12"/>
-      <c r="L21" s="12"/>
-      <c r="M21" s="12"/>
-      <c r="N21" s="12"/>
-      <c r="O21" s="46"/>
+      <c r="A21" s="13" t="s">
+        <v>116</v>
+      </c>
+      <c r="B21" s="14"/>
+      <c r="C21" s="14"/>
+      <c r="D21" s="14"/>
+      <c r="E21" s="14"/>
+      <c r="F21" s="14"/>
+      <c r="G21" s="14"/>
+      <c r="H21" s="14"/>
+      <c r="I21" s="14"/>
+      <c r="J21" s="14"/>
+      <c r="K21" s="14"/>
+      <c r="L21" s="14"/>
+      <c r="M21" s="14"/>
+      <c r="N21" s="14"/>
+      <c r="O21" s="47"/>
     </row>
     <row r="22" s="3" customFormat="1" spans="1:15">
-      <c r="A22" s="13" t="s">
+      <c r="A22" s="15" t="s">
+        <v>29</v>
+      </c>
+      <c r="B22" s="16" t="s">
+        <v>117</v>
+      </c>
+      <c r="C22" s="17"/>
+      <c r="D22" s="16" t="s">
+        <v>88</v>
+      </c>
+      <c r="E22" s="15" t="s">
+        <v>54</v>
+      </c>
+      <c r="F22" s="15" t="s">
+        <v>56</v>
+      </c>
+      <c r="G22" s="15" t="s">
+        <v>118</v>
+      </c>
+      <c r="H22" s="15"/>
+      <c r="I22" s="15"/>
+      <c r="J22" s="16" t="s">
         <v>119</v>
       </c>
-      <c r="B22" s="14"/>
-      <c r="C22" s="14"/>
-      <c r="D22" s="14"/>
-      <c r="E22" s="14"/>
-      <c r="F22" s="14"/>
-      <c r="G22" s="14"/>
-      <c r="H22" s="14"/>
-      <c r="I22" s="14"/>
-      <c r="J22" s="14"/>
-      <c r="K22" s="14"/>
-      <c r="L22" s="14"/>
-      <c r="M22" s="14"/>
-      <c r="N22" s="14"/>
-      <c r="O22" s="47"/>
+      <c r="K22" s="36"/>
+      <c r="L22" s="36"/>
+      <c r="M22" s="36"/>
+      <c r="N22" s="36"/>
+      <c r="O22" s="17"/>
     </row>
     <row r="23" s="3" customFormat="1" spans="1:15">
-      <c r="A23" s="15" t="s">
-        <v>29</v>
-      </c>
-      <c r="B23" s="16" t="s">
-        <v>120</v>
-      </c>
-      <c r="C23" s="17"/>
-      <c r="D23" s="16" t="s">
-        <v>88</v>
-      </c>
-      <c r="E23" s="15" t="s">
-        <v>54</v>
-      </c>
-      <c r="F23" s="15" t="s">
-        <v>56</v>
-      </c>
-      <c r="G23" s="15" t="s">
-        <v>121</v>
-      </c>
-      <c r="H23" s="15"/>
-      <c r="I23" s="15"/>
-      <c r="J23" s="16" t="s">
-        <v>122</v>
-      </c>
-      <c r="K23" s="36"/>
-      <c r="L23" s="36"/>
-      <c r="M23" s="36"/>
-      <c r="N23" s="36"/>
-      <c r="O23" s="17"/>
+      <c r="A23" s="18"/>
+      <c r="B23" s="18"/>
+      <c r="C23" s="18"/>
+      <c r="D23" s="18"/>
+      <c r="E23" s="27"/>
+      <c r="F23" s="27"/>
+      <c r="G23" s="38"/>
+      <c r="H23" s="39"/>
+      <c r="I23" s="48"/>
+      <c r="J23" s="38"/>
+      <c r="K23" s="39"/>
+      <c r="L23" s="39"/>
+      <c r="M23" s="39"/>
+      <c r="N23" s="39"/>
+      <c r="O23" s="48"/>
     </row>
     <row r="24" s="3" customFormat="1" spans="1:15">
       <c r="A24" s="18"/>
@@ -3299,75 +3278,81 @@
       <c r="N26" s="39"/>
       <c r="O26" s="48"/>
     </row>
-    <row r="27" s="3" customFormat="1" spans="1:15">
-      <c r="A27" s="18"/>
-      <c r="B27" s="18"/>
-      <c r="C27" s="18"/>
-      <c r="D27" s="18"/>
-      <c r="E27" s="27"/>
-      <c r="F27" s="27"/>
-      <c r="G27" s="38"/>
-      <c r="H27" s="39"/>
-      <c r="I27" s="48"/>
-      <c r="J27" s="38"/>
-      <c r="K27" s="39"/>
-      <c r="L27" s="39"/>
-      <c r="M27" s="39"/>
-      <c r="N27" s="39"/>
-      <c r="O27" s="48"/>
+    <row r="27" s="1" customFormat="1" spans="1:15">
+      <c r="A27" s="20"/>
+      <c r="B27" s="21"/>
+      <c r="C27" s="21"/>
+      <c r="D27" s="21"/>
+      <c r="E27" s="21"/>
+      <c r="F27" s="21"/>
+      <c r="G27" s="21"/>
+      <c r="H27" s="21"/>
+      <c r="I27" s="21"/>
+      <c r="J27" s="21"/>
+      <c r="K27" s="21"/>
+      <c r="L27" s="21"/>
+      <c r="M27" s="21"/>
+      <c r="N27" s="21"/>
+      <c r="O27" s="49"/>
     </row>
     <row r="28" s="1" customFormat="1" spans="1:15">
-      <c r="A28" s="20"/>
-      <c r="B28" s="21"/>
-      <c r="C28" s="21"/>
-      <c r="D28" s="21"/>
-      <c r="E28" s="21"/>
-      <c r="F28" s="21"/>
-      <c r="G28" s="21"/>
-      <c r="H28" s="21"/>
-      <c r="I28" s="21"/>
-      <c r="J28" s="21"/>
-      <c r="K28" s="21"/>
-      <c r="L28" s="21"/>
-      <c r="M28" s="21"/>
-      <c r="N28" s="21"/>
-      <c r="O28" s="49"/>
+      <c r="A28" s="8" t="s">
+        <v>120</v>
+      </c>
+      <c r="B28" s="8"/>
+      <c r="C28" s="8"/>
+      <c r="D28" s="8"/>
+      <c r="E28" s="8"/>
+      <c r="F28" s="8"/>
+      <c r="G28" s="8"/>
+      <c r="H28" s="8"/>
+      <c r="I28" s="8"/>
+      <c r="J28" s="8"/>
+      <c r="K28" s="8"/>
+      <c r="L28" s="8"/>
+      <c r="M28" s="8"/>
+      <c r="N28" s="8"/>
+      <c r="O28" s="8"/>
     </row>
     <row r="29" s="1" customFormat="1" spans="1:15">
-      <c r="A29" s="8" t="s">
+      <c r="A29" s="22"/>
+      <c r="B29" s="4" t="s">
+        <v>121</v>
+      </c>
+      <c r="C29" s="4"/>
+      <c r="D29" s="5"/>
+      <c r="E29" s="5"/>
+      <c r="F29" s="4" t="s">
+        <v>122</v>
+      </c>
+      <c r="G29" s="5"/>
+      <c r="H29" s="5"/>
+      <c r="I29" s="5"/>
+      <c r="J29" s="4" t="s">
         <v>123</v>
       </c>
-      <c r="B29" s="8"/>
-      <c r="C29" s="8"/>
-      <c r="D29" s="8"/>
-      <c r="E29" s="8"/>
-      <c r="F29" s="8"/>
-      <c r="G29" s="8"/>
-      <c r="H29" s="8"/>
-      <c r="I29" s="8"/>
-      <c r="J29" s="8"/>
-      <c r="K29" s="8"/>
-      <c r="L29" s="8"/>
-      <c r="M29" s="8"/>
-      <c r="N29" s="8"/>
-      <c r="O29" s="8"/>
+      <c r="K29" s="4"/>
+      <c r="L29" s="5"/>
+      <c r="M29" s="5"/>
+      <c r="N29" s="5"/>
+      <c r="O29" s="5"/>
     </row>
     <row r="30" s="1" customFormat="1" spans="1:15">
       <c r="A30" s="22"/>
       <c r="B30" s="4" t="s">
-        <v>124</v>
+        <v>54</v>
       </c>
       <c r="C30" s="4"/>
       <c r="D30" s="5"/>
       <c r="E30" s="5"/>
       <c r="F30" s="4" t="s">
-        <v>125</v>
+        <v>56</v>
       </c>
       <c r="G30" s="5"/>
       <c r="H30" s="5"/>
       <c r="I30" s="5"/>
       <c r="J30" s="4" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="K30" s="4"/>
       <c r="L30" s="5"/>
@@ -3378,20 +3363,18 @@
     <row r="31" s="1" customFormat="1" spans="1:15">
       <c r="A31" s="22"/>
       <c r="B31" s="4" t="s">
-        <v>54</v>
+        <v>125</v>
       </c>
       <c r="C31" s="4"/>
       <c r="D31" s="5"/>
       <c r="E31" s="5"/>
       <c r="F31" s="4" t="s">
-        <v>56</v>
-      </c>
-      <c r="G31" s="5"/>
-      <c r="H31" s="5"/>
-      <c r="I31" s="5"/>
-      <c r="J31" s="4" t="s">
-        <v>127</v>
-      </c>
+        <v>126</v>
+      </c>
+      <c r="G31" s="9"/>
+      <c r="H31" s="9"/>
+      <c r="I31" s="9"/>
+      <c r="J31" s="4"/>
       <c r="K31" s="4"/>
       <c r="L31" s="5"/>
       <c r="M31" s="5"/>
@@ -3401,18 +3384,18 @@
     <row r="32" s="1" customFormat="1" spans="1:15">
       <c r="A32" s="22"/>
       <c r="B32" s="4" t="s">
-        <v>128</v>
+        <v>87</v>
       </c>
       <c r="C32" s="4"/>
       <c r="D32" s="5"/>
       <c r="E32" s="5"/>
-      <c r="F32" s="4" t="s">
-        <v>129</v>
-      </c>
-      <c r="G32" s="9"/>
-      <c r="H32" s="9"/>
-      <c r="I32" s="9"/>
-      <c r="J32" s="4"/>
+      <c r="F32" s="5"/>
+      <c r="G32" s="5"/>
+      <c r="H32" s="5"/>
+      <c r="I32" s="5"/>
+      <c r="J32" s="4" t="s">
+        <v>86</v>
+      </c>
       <c r="K32" s="4"/>
       <c r="L32" s="5"/>
       <c r="M32" s="5"/>
@@ -3421,92 +3404,88 @@
     </row>
     <row r="33" s="1" customFormat="1" spans="1:15">
       <c r="A33" s="22"/>
-      <c r="B33" s="4" t="s">
-        <v>87</v>
-      </c>
-      <c r="C33" s="4"/>
-      <c r="D33" s="5"/>
-      <c r="E33" s="5"/>
-      <c r="F33" s="5"/>
-      <c r="G33" s="5"/>
-      <c r="H33" s="5"/>
-      <c r="I33" s="5"/>
-      <c r="J33" s="4" t="s">
-        <v>86</v>
-      </c>
-      <c r="K33" s="4"/>
-      <c r="L33" s="5"/>
-      <c r="M33" s="5"/>
-      <c r="N33" s="5"/>
-      <c r="O33" s="5"/>
+      <c r="B33" s="23" t="s">
+        <v>127</v>
+      </c>
+      <c r="C33" s="23"/>
+      <c r="D33" s="23"/>
+      <c r="E33" s="23"/>
+      <c r="F33" s="23"/>
+      <c r="G33" s="23"/>
+      <c r="H33" s="23"/>
+      <c r="I33" s="23"/>
+      <c r="J33" s="40"/>
+      <c r="K33" s="41"/>
+      <c r="L33" s="40"/>
+      <c r="M33" s="50"/>
+      <c r="N33" s="50"/>
+      <c r="O33" s="41"/>
     </row>
     <row r="34" s="1" customFormat="1" spans="1:15">
       <c r="A34" s="22"/>
-      <c r="B34" s="23" t="s">
+      <c r="B34" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="C34" s="4" t="s">
+        <v>128</v>
+      </c>
+      <c r="D34" s="4"/>
+      <c r="E34" s="4" t="s">
+        <v>129</v>
+      </c>
+      <c r="F34" s="4" t="s">
         <v>130</v>
       </c>
-      <c r="C34" s="23"/>
-      <c r="D34" s="23"/>
-      <c r="E34" s="23"/>
-      <c r="F34" s="23"/>
-      <c r="G34" s="23"/>
-      <c r="H34" s="23"/>
-      <c r="I34" s="23"/>
-      <c r="J34" s="40"/>
-      <c r="K34" s="41"/>
-      <c r="L34" s="40"/>
-      <c r="M34" s="50"/>
-      <c r="N34" s="50"/>
-      <c r="O34" s="41"/>
+      <c r="G34" s="4"/>
+      <c r="H34" s="4" t="s">
+        <v>131</v>
+      </c>
+      <c r="I34" s="4"/>
+      <c r="J34" s="4"/>
+      <c r="K34" s="4"/>
+      <c r="L34" s="4"/>
+      <c r="M34" s="4"/>
+      <c r="N34" s="4"/>
+      <c r="O34" s="4"/>
     </row>
     <row r="35" s="1" customFormat="1" spans="1:15">
       <c r="A35" s="22"/>
-      <c r="B35" s="4" t="s">
-        <v>29</v>
-      </c>
-      <c r="C35" s="4" t="s">
-        <v>131</v>
-      </c>
-      <c r="D35" s="4"/>
-      <c r="E35" s="4" t="s">
-        <v>132</v>
-      </c>
-      <c r="F35" s="4" t="s">
-        <v>133</v>
-      </c>
-      <c r="G35" s="4"/>
-      <c r="H35" s="4" t="s">
-        <v>134</v>
-      </c>
-      <c r="I35" s="4"/>
-      <c r="J35" s="4"/>
-      <c r="K35" s="4"/>
-      <c r="L35" s="4"/>
-      <c r="M35" s="4"/>
-      <c r="N35" s="4"/>
-      <c r="O35" s="4"/>
+      <c r="B35" s="9">
+        <v>1</v>
+      </c>
+      <c r="C35" s="5"/>
+      <c r="D35" s="5"/>
+      <c r="E35" s="5"/>
+      <c r="F35" s="5"/>
+      <c r="G35" s="5"/>
+      <c r="H35" s="5"/>
+      <c r="I35" s="5"/>
+      <c r="J35" s="9"/>
+      <c r="K35" s="9"/>
+      <c r="L35" s="9"/>
+      <c r="M35" s="9"/>
+      <c r="N35" s="9"/>
+      <c r="O35" s="9"/>
     </row>
     <row r="36" s="1" customFormat="1" spans="1:15">
-      <c r="A36" s="22"/>
-      <c r="B36" s="9">
-        <v>1</v>
-      </c>
-      <c r="C36" s="5"/>
-      <c r="D36" s="5"/>
+      <c r="A36" s="24"/>
+      <c r="B36" s="9"/>
+      <c r="C36" s="6"/>
+      <c r="D36" s="25"/>
       <c r="E36" s="5"/>
-      <c r="F36" s="5"/>
-      <c r="G36" s="5"/>
-      <c r="H36" s="5"/>
-      <c r="I36" s="5"/>
-      <c r="J36" s="9"/>
-      <c r="K36" s="9"/>
-      <c r="L36" s="9"/>
-      <c r="M36" s="9"/>
-      <c r="N36" s="9"/>
-      <c r="O36" s="9"/>
+      <c r="F36" s="6"/>
+      <c r="G36" s="30"/>
+      <c r="H36" s="6"/>
+      <c r="I36" s="30"/>
+      <c r="J36" s="42"/>
+      <c r="K36" s="43"/>
+      <c r="L36" s="42"/>
+      <c r="M36" s="51"/>
+      <c r="N36" s="51"/>
+      <c r="O36" s="43"/>
     </row>
     <row r="37" s="1" customFormat="1" spans="1:15">
-      <c r="A37" s="24"/>
+      <c r="A37" s="26"/>
       <c r="B37" s="9"/>
       <c r="C37" s="6"/>
       <c r="D37" s="25"/>
@@ -3523,38 +3502,44 @@
       <c r="O37" s="43"/>
     </row>
     <row r="38" s="1" customFormat="1" spans="1:15">
-      <c r="A38" s="26"/>
-      <c r="B38" s="9"/>
-      <c r="C38" s="6"/>
-      <c r="D38" s="25"/>
+      <c r="A38" s="22"/>
+      <c r="B38" s="4" t="s">
+        <v>121</v>
+      </c>
+      <c r="C38" s="4"/>
+      <c r="D38" s="5"/>
       <c r="E38" s="5"/>
-      <c r="F38" s="6"/>
-      <c r="G38" s="30"/>
-      <c r="H38" s="6"/>
-      <c r="I38" s="30"/>
-      <c r="J38" s="42"/>
-      <c r="K38" s="43"/>
-      <c r="L38" s="42"/>
-      <c r="M38" s="51"/>
-      <c r="N38" s="51"/>
-      <c r="O38" s="43"/>
+      <c r="F38" s="4" t="s">
+        <v>122</v>
+      </c>
+      <c r="G38" s="5"/>
+      <c r="H38" s="5"/>
+      <c r="I38" s="5"/>
+      <c r="J38" s="4" t="s">
+        <v>123</v>
+      </c>
+      <c r="K38" s="4"/>
+      <c r="L38" s="5"/>
+      <c r="M38" s="5"/>
+      <c r="N38" s="5"/>
+      <c r="O38" s="5"/>
     </row>
     <row r="39" s="1" customFormat="1" spans="1:15">
       <c r="A39" s="22"/>
       <c r="B39" s="4" t="s">
-        <v>124</v>
+        <v>54</v>
       </c>
       <c r="C39" s="4"/>
       <c r="D39" s="5"/>
       <c r="E39" s="5"/>
       <c r="F39" s="4" t="s">
-        <v>125</v>
+        <v>56</v>
       </c>
       <c r="G39" s="5"/>
       <c r="H39" s="5"/>
       <c r="I39" s="5"/>
       <c r="J39" s="4" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="K39" s="4"/>
       <c r="L39" s="5"/>
@@ -3565,20 +3550,18 @@
     <row r="40" s="1" customFormat="1" spans="1:15">
       <c r="A40" s="22"/>
       <c r="B40" s="4" t="s">
-        <v>54</v>
+        <v>125</v>
       </c>
       <c r="C40" s="4"/>
       <c r="D40" s="5"/>
       <c r="E40" s="5"/>
       <c r="F40" s="4" t="s">
-        <v>56</v>
-      </c>
-      <c r="G40" s="5"/>
-      <c r="H40" s="5"/>
-      <c r="I40" s="5"/>
-      <c r="J40" s="4" t="s">
-        <v>127</v>
-      </c>
+        <v>126</v>
+      </c>
+      <c r="G40" s="9"/>
+      <c r="H40" s="9"/>
+      <c r="I40" s="9"/>
+      <c r="J40" s="4"/>
       <c r="K40" s="4"/>
       <c r="L40" s="5"/>
       <c r="M40" s="5"/>
@@ -3588,18 +3571,18 @@
     <row r="41" s="1" customFormat="1" spans="1:15">
       <c r="A41" s="22"/>
       <c r="B41" s="4" t="s">
-        <v>128</v>
+        <v>87</v>
       </c>
       <c r="C41" s="4"/>
       <c r="D41" s="5"/>
       <c r="E41" s="5"/>
-      <c r="F41" s="4" t="s">
-        <v>129</v>
-      </c>
-      <c r="G41" s="9"/>
-      <c r="H41" s="9"/>
-      <c r="I41" s="9"/>
-      <c r="J41" s="4"/>
+      <c r="F41" s="5"/>
+      <c r="G41" s="5"/>
+      <c r="H41" s="5"/>
+      <c r="I41" s="5"/>
+      <c r="J41" s="4" t="s">
+        <v>86</v>
+      </c>
       <c r="K41" s="4"/>
       <c r="L41" s="5"/>
       <c r="M41" s="5"/>
@@ -3608,92 +3591,88 @@
     </row>
     <row r="42" s="1" customFormat="1" spans="1:15">
       <c r="A42" s="22"/>
-      <c r="B42" s="4" t="s">
-        <v>87</v>
-      </c>
-      <c r="C42" s="4"/>
-      <c r="D42" s="5"/>
-      <c r="E42" s="5"/>
-      <c r="F42" s="5"/>
-      <c r="G42" s="5"/>
-      <c r="H42" s="5"/>
-      <c r="I42" s="5"/>
-      <c r="J42" s="4" t="s">
-        <v>86</v>
-      </c>
-      <c r="K42" s="4"/>
-      <c r="L42" s="5"/>
-      <c r="M42" s="5"/>
-      <c r="N42" s="5"/>
-      <c r="O42" s="5"/>
+      <c r="B42" s="23" t="s">
+        <v>127</v>
+      </c>
+      <c r="C42" s="23"/>
+      <c r="D42" s="23"/>
+      <c r="E42" s="23"/>
+      <c r="F42" s="23"/>
+      <c r="G42" s="23"/>
+      <c r="H42" s="23"/>
+      <c r="I42" s="23"/>
+      <c r="J42" s="40"/>
+      <c r="K42" s="41"/>
+      <c r="L42" s="40"/>
+      <c r="M42" s="50"/>
+      <c r="N42" s="50"/>
+      <c r="O42" s="41"/>
     </row>
     <row r="43" s="1" customFormat="1" spans="1:15">
       <c r="A43" s="22"/>
-      <c r="B43" s="23" t="s">
+      <c r="B43" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="C43" s="4" t="s">
+        <v>128</v>
+      </c>
+      <c r="D43" s="4"/>
+      <c r="E43" s="4" t="s">
+        <v>129</v>
+      </c>
+      <c r="F43" s="4" t="s">
         <v>130</v>
       </c>
-      <c r="C43" s="23"/>
-      <c r="D43" s="23"/>
-      <c r="E43" s="23"/>
-      <c r="F43" s="23"/>
-      <c r="G43" s="23"/>
-      <c r="H43" s="23"/>
-      <c r="I43" s="23"/>
-      <c r="J43" s="40"/>
-      <c r="K43" s="41"/>
-      <c r="L43" s="40"/>
-      <c r="M43" s="50"/>
-      <c r="N43" s="50"/>
-      <c r="O43" s="41"/>
+      <c r="G43" s="4"/>
+      <c r="H43" s="4" t="s">
+        <v>131</v>
+      </c>
+      <c r="I43" s="4"/>
+      <c r="J43" s="4"/>
+      <c r="K43" s="4"/>
+      <c r="L43" s="4"/>
+      <c r="M43" s="4"/>
+      <c r="N43" s="4"/>
+      <c r="O43" s="4"/>
     </row>
     <row r="44" s="1" customFormat="1" spans="1:15">
       <c r="A44" s="22"/>
-      <c r="B44" s="4" t="s">
-        <v>29</v>
-      </c>
-      <c r="C44" s="4" t="s">
-        <v>131</v>
-      </c>
-      <c r="D44" s="4"/>
-      <c r="E44" s="4" t="s">
-        <v>132</v>
-      </c>
-      <c r="F44" s="4" t="s">
-        <v>133</v>
-      </c>
-      <c r="G44" s="4"/>
-      <c r="H44" s="4" t="s">
-        <v>134</v>
-      </c>
-      <c r="I44" s="4"/>
-      <c r="J44" s="4"/>
-      <c r="K44" s="4"/>
-      <c r="L44" s="4"/>
-      <c r="M44" s="4"/>
-      <c r="N44" s="4"/>
-      <c r="O44" s="4"/>
+      <c r="B44" s="9">
+        <v>1</v>
+      </c>
+      <c r="C44" s="5"/>
+      <c r="D44" s="5"/>
+      <c r="E44" s="5"/>
+      <c r="F44" s="5"/>
+      <c r="G44" s="5"/>
+      <c r="H44" s="5"/>
+      <c r="I44" s="5"/>
+      <c r="J44" s="9"/>
+      <c r="K44" s="9"/>
+      <c r="L44" s="9"/>
+      <c r="M44" s="9"/>
+      <c r="N44" s="9"/>
+      <c r="O44" s="9"/>
     </row>
     <row r="45" s="1" customFormat="1" spans="1:15">
-      <c r="A45" s="22"/>
-      <c r="B45" s="9">
-        <v>1</v>
-      </c>
-      <c r="C45" s="5"/>
-      <c r="D45" s="5"/>
+      <c r="A45" s="24"/>
+      <c r="B45" s="9"/>
+      <c r="C45" s="6"/>
+      <c r="D45" s="25"/>
       <c r="E45" s="5"/>
-      <c r="F45" s="5"/>
-      <c r="G45" s="5"/>
-      <c r="H45" s="5"/>
-      <c r="I45" s="5"/>
-      <c r="J45" s="9"/>
-      <c r="K45" s="9"/>
-      <c r="L45" s="9"/>
-      <c r="M45" s="9"/>
-      <c r="N45" s="9"/>
-      <c r="O45" s="9"/>
+      <c r="F45" s="6"/>
+      <c r="G45" s="30"/>
+      <c r="H45" s="6"/>
+      <c r="I45" s="30"/>
+      <c r="J45" s="42"/>
+      <c r="K45" s="43"/>
+      <c r="L45" s="42"/>
+      <c r="M45" s="51"/>
+      <c r="N45" s="51"/>
+      <c r="O45" s="43"/>
     </row>
     <row r="46" s="1" customFormat="1" spans="1:15">
-      <c r="A46" s="24"/>
+      <c r="A46" s="26"/>
       <c r="B46" s="9"/>
       <c r="C46" s="6"/>
       <c r="D46" s="25"/>
@@ -3708,23 +3687,6 @@
       <c r="M46" s="51"/>
       <c r="N46" s="51"/>
       <c r="O46" s="43"/>
-    </row>
-    <row r="47" s="1" customFormat="1" spans="1:15">
-      <c r="A47" s="26"/>
-      <c r="B47" s="9"/>
-      <c r="C47" s="6"/>
-      <c r="D47" s="25"/>
-      <c r="E47" s="5"/>
-      <c r="F47" s="6"/>
-      <c r="G47" s="30"/>
-      <c r="H47" s="6"/>
-      <c r="I47" s="30"/>
-      <c r="J47" s="42"/>
-      <c r="K47" s="43"/>
-      <c r="L47" s="42"/>
-      <c r="M47" s="51"/>
-      <c r="N47" s="51"/>
-      <c r="O47" s="43"/>
     </row>
   </sheetData>
   <mergeCells count="118">
@@ -3741,8 +3703,11 @@
     <mergeCell ref="D4:O4"/>
     <mergeCell ref="A5:O5"/>
     <mergeCell ref="A6:O6"/>
+    <mergeCell ref="A20:O20"/>
     <mergeCell ref="A21:O21"/>
-    <mergeCell ref="A22:O22"/>
+    <mergeCell ref="B22:C22"/>
+    <mergeCell ref="G22:I22"/>
+    <mergeCell ref="J22:O22"/>
     <mergeCell ref="B23:C23"/>
     <mergeCell ref="G23:I23"/>
     <mergeCell ref="J23:O23"/>
@@ -3755,11 +3720,13 @@
     <mergeCell ref="B26:C26"/>
     <mergeCell ref="G26:I26"/>
     <mergeCell ref="J26:O26"/>
-    <mergeCell ref="B27:C27"/>
-    <mergeCell ref="G27:I27"/>
-    <mergeCell ref="J27:O27"/>
+    <mergeCell ref="A27:O27"/>
     <mergeCell ref="A28:O28"/>
-    <mergeCell ref="A29:O29"/>
+    <mergeCell ref="B29:C29"/>
+    <mergeCell ref="D29:E29"/>
+    <mergeCell ref="G29:I29"/>
+    <mergeCell ref="J29:K29"/>
+    <mergeCell ref="L29:O29"/>
     <mergeCell ref="B30:C30"/>
     <mergeCell ref="D30:E30"/>
     <mergeCell ref="G30:I30"/>
@@ -3771,15 +3738,15 @@
     <mergeCell ref="J31:K31"/>
     <mergeCell ref="L31:O31"/>
     <mergeCell ref="B32:C32"/>
-    <mergeCell ref="D32:E32"/>
-    <mergeCell ref="G32:I32"/>
+    <mergeCell ref="D32:I32"/>
     <mergeCell ref="J32:K32"/>
     <mergeCell ref="L32:O32"/>
-    <mergeCell ref="B33:C33"/>
-    <mergeCell ref="D33:I33"/>
+    <mergeCell ref="B33:I33"/>
     <mergeCell ref="J33:K33"/>
     <mergeCell ref="L33:O33"/>
-    <mergeCell ref="B34:I34"/>
+    <mergeCell ref="C34:D34"/>
+    <mergeCell ref="F34:G34"/>
+    <mergeCell ref="H34:I34"/>
     <mergeCell ref="J34:K34"/>
     <mergeCell ref="L34:O34"/>
     <mergeCell ref="C35:D35"/>
@@ -3797,9 +3764,9 @@
     <mergeCell ref="H37:I37"/>
     <mergeCell ref="J37:K37"/>
     <mergeCell ref="L37:O37"/>
-    <mergeCell ref="C38:D38"/>
-    <mergeCell ref="F38:G38"/>
-    <mergeCell ref="H38:I38"/>
+    <mergeCell ref="B38:C38"/>
+    <mergeCell ref="D38:E38"/>
+    <mergeCell ref="G38:I38"/>
     <mergeCell ref="J38:K38"/>
     <mergeCell ref="L38:O38"/>
     <mergeCell ref="B39:C39"/>
@@ -3813,15 +3780,15 @@
     <mergeCell ref="J40:K40"/>
     <mergeCell ref="L40:O40"/>
     <mergeCell ref="B41:C41"/>
-    <mergeCell ref="D41:E41"/>
-    <mergeCell ref="G41:I41"/>
+    <mergeCell ref="D41:I41"/>
     <mergeCell ref="J41:K41"/>
     <mergeCell ref="L41:O41"/>
-    <mergeCell ref="B42:C42"/>
-    <mergeCell ref="D42:I42"/>
+    <mergeCell ref="B42:I42"/>
     <mergeCell ref="J42:K42"/>
     <mergeCell ref="L42:O42"/>
-    <mergeCell ref="B43:I43"/>
+    <mergeCell ref="C43:D43"/>
+    <mergeCell ref="F43:G43"/>
+    <mergeCell ref="H43:I43"/>
     <mergeCell ref="J43:K43"/>
     <mergeCell ref="L43:O43"/>
     <mergeCell ref="C44:D44"/>
@@ -3839,13 +3806,8 @@
     <mergeCell ref="H46:I46"/>
     <mergeCell ref="J46:K46"/>
     <mergeCell ref="L46:O46"/>
-    <mergeCell ref="C47:D47"/>
-    <mergeCell ref="F47:G47"/>
-    <mergeCell ref="H47:I47"/>
-    <mergeCell ref="J47:K47"/>
-    <mergeCell ref="L47:O47"/>
-    <mergeCell ref="A30:A38"/>
-    <mergeCell ref="A39:A47"/>
+    <mergeCell ref="A29:A37"/>
+    <mergeCell ref="A38:A46"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>
@@ -3879,7 +3841,7 @@
       <c r="B1" s="4"/>
       <c r="C1" s="4"/>
       <c r="D1" s="5" t="s">
-        <v>135</v>
+        <v>132</v>
       </c>
       <c r="E1" s="5"/>
       <c r="F1" s="5"/>
@@ -3887,7 +3849,7 @@
         <v>82</v>
       </c>
       <c r="H1" s="6" t="s">
-        <v>136</v>
+        <v>133</v>
       </c>
       <c r="I1" s="25"/>
       <c r="J1" s="25"/>
@@ -3904,7 +3866,7 @@
       <c r="B2" s="4"/>
       <c r="C2" s="4"/>
       <c r="D2" s="5" t="s">
-        <v>137</v>
+        <v>134</v>
       </c>
       <c r="E2" s="5"/>
       <c r="F2" s="5"/>
@@ -3948,7 +3910,7 @@
       <c r="B4" s="4"/>
       <c r="C4" s="4"/>
       <c r="D4" s="6" t="s">
-        <v>138</v>
+        <v>135</v>
       </c>
       <c r="E4" s="25"/>
       <c r="F4" s="25"/>
@@ -4085,11 +4047,11 @@
       <c r="B9" s="9"/>
       <c r="C9" s="9"/>
       <c r="D9" s="5" t="s">
-        <v>139</v>
+        <v>136</v>
       </c>
       <c r="E9" s="9"/>
       <c r="F9" s="5" t="s">
-        <v>140</v>
+        <v>137</v>
       </c>
       <c r="G9" s="5"/>
       <c r="H9" s="9" t="s">
@@ -4114,11 +4076,11 @@
       <c r="B10" s="10"/>
       <c r="C10" s="10"/>
       <c r="D10" s="5" t="s">
-        <v>141</v>
+        <v>138</v>
       </c>
       <c r="E10" s="9"/>
       <c r="F10" s="5" t="s">
-        <v>142</v>
+        <v>139</v>
       </c>
       <c r="G10" s="5"/>
       <c r="H10" s="9" t="s">
@@ -4143,11 +4105,11 @@
       <c r="B11" s="9"/>
       <c r="C11" s="9"/>
       <c r="D11" s="5" t="s">
-        <v>143</v>
+        <v>140</v>
       </c>
       <c r="E11" s="9"/>
       <c r="F11" s="5" t="s">
-        <v>144</v>
+        <v>141</v>
       </c>
       <c r="G11" s="5"/>
       <c r="H11" s="9" t="s">
@@ -4341,7 +4303,7 @@
     </row>
     <row r="22" s="3" customFormat="1" spans="1:15">
       <c r="A22" s="13" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
       <c r="B22" s="14"/>
       <c r="C22" s="14"/>
@@ -4363,7 +4325,7 @@
         <v>29</v>
       </c>
       <c r="B23" s="16" t="s">
-        <v>120</v>
+        <v>117</v>
       </c>
       <c r="C23" s="17"/>
       <c r="D23" s="16" t="s">
@@ -4376,12 +4338,12 @@
         <v>56</v>
       </c>
       <c r="G23" s="15" t="s">
-        <v>121</v>
+        <v>118</v>
       </c>
       <c r="H23" s="15"/>
       <c r="I23" s="15"/>
       <c r="J23" s="16" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="K23" s="36"/>
       <c r="L23" s="36"/>
@@ -4394,16 +4356,16 @@
         <v>1</v>
       </c>
       <c r="B24" s="19" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="C24" s="19"/>
       <c r="D24" s="18" t="s">
-        <v>146</v>
+        <v>143</v>
       </c>
       <c r="E24" s="27"/>
       <c r="F24" s="27"/>
       <c r="G24" s="28" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="H24" s="29"/>
       <c r="I24" s="37"/>
@@ -4484,7 +4446,7 @@
     </row>
     <row r="29" s="1" customFormat="1" spans="1:15">
       <c r="A29" s="8" t="s">
-        <v>123</v>
+        <v>120</v>
       </c>
       <c r="B29" s="8"/>
       <c r="C29" s="8"/>
@@ -4506,23 +4468,23 @@
         <v>1</v>
       </c>
       <c r="B30" s="4" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
       <c r="C30" s="4"/>
       <c r="D30" s="5" t="s">
-        <v>147</v>
+        <v>144</v>
       </c>
       <c r="E30" s="5"/>
       <c r="F30" s="4" t="s">
-        <v>125</v>
+        <v>122</v>
       </c>
       <c r="G30" s="5" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="H30" s="5"/>
       <c r="I30" s="5"/>
       <c r="J30" s="4" t="s">
-        <v>126</v>
+        <v>123</v>
       </c>
       <c r="K30" s="4"/>
       <c r="L30" s="5" t="s">
@@ -4539,7 +4501,7 @@
       </c>
       <c r="C31" s="4"/>
       <c r="D31" s="5" t="s">
-        <v>149</v>
+        <v>146</v>
       </c>
       <c r="E31" s="5"/>
       <c r="F31" s="4" t="s">
@@ -4549,11 +4511,11 @@
       <c r="H31" s="5"/>
       <c r="I31" s="5"/>
       <c r="J31" s="4" t="s">
-        <v>127</v>
+        <v>124</v>
       </c>
       <c r="K31" s="4"/>
       <c r="L31" s="5" t="s">
-        <v>150</v>
+        <v>147</v>
       </c>
       <c r="M31" s="5"/>
       <c r="N31" s="5"/>
@@ -4562,13 +4524,13 @@
     <row r="32" s="1" customFormat="1" spans="1:15">
       <c r="A32" s="22"/>
       <c r="B32" s="4" t="s">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="C32" s="4"/>
       <c r="D32" s="5"/>
       <c r="E32" s="5"/>
       <c r="F32" s="4" t="s">
-        <v>129</v>
+        <v>126</v>
       </c>
       <c r="G32" s="9"/>
       <c r="H32" s="9"/>
@@ -4597,7 +4559,7 @@
       </c>
       <c r="K33" s="4"/>
       <c r="L33" s="5" t="s">
-        <v>151</v>
+        <v>148</v>
       </c>
       <c r="M33" s="5"/>
       <c r="N33" s="5"/>
@@ -4606,7 +4568,7 @@
     <row r="34" s="1" customFormat="1" spans="1:15">
       <c r="A34" s="22"/>
       <c r="B34" s="23" t="s">
-        <v>130</v>
+        <v>127</v>
       </c>
       <c r="C34" s="23"/>
       <c r="D34" s="23"/>
@@ -4628,18 +4590,18 @@
         <v>29</v>
       </c>
       <c r="C35" s="4" t="s">
-        <v>131</v>
+        <v>128</v>
       </c>
       <c r="D35" s="4"/>
       <c r="E35" s="4" t="s">
-        <v>132</v>
+        <v>129</v>
       </c>
       <c r="F35" s="4" t="s">
-        <v>133</v>
+        <v>130</v>
       </c>
       <c r="G35" s="4"/>
       <c r="H35" s="4" t="s">
-        <v>134</v>
+        <v>131</v>
       </c>
       <c r="I35" s="4"/>
       <c r="J35" s="4"/>
@@ -4655,7 +4617,7 @@
         <v>1</v>
       </c>
       <c r="C36" s="5" t="s">
-        <v>152</v>
+        <v>149</v>
       </c>
       <c r="D36" s="5"/>
       <c r="E36" s="5"/>
@@ -4711,23 +4673,23 @@
         <v>2</v>
       </c>
       <c r="B39" s="4" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
       <c r="C39" s="4"/>
       <c r="D39" s="5" t="s">
-        <v>153</v>
+        <v>150</v>
       </c>
       <c r="E39" s="5"/>
       <c r="F39" s="4" t="s">
-        <v>125</v>
+        <v>122</v>
       </c>
       <c r="G39" s="5" t="s">
-        <v>154</v>
+        <v>151</v>
       </c>
       <c r="H39" s="5"/>
       <c r="I39" s="5"/>
       <c r="J39" s="4" t="s">
-        <v>126</v>
+        <v>123</v>
       </c>
       <c r="K39" s="4"/>
       <c r="L39" s="5" t="s">
@@ -4744,7 +4706,7 @@
       </c>
       <c r="C40" s="4"/>
       <c r="D40" s="5" t="s">
-        <v>155</v>
+        <v>152</v>
       </c>
       <c r="E40" s="5"/>
       <c r="F40" s="4" t="s">
@@ -4754,11 +4716,11 @@
       <c r="H40" s="5"/>
       <c r="I40" s="5"/>
       <c r="J40" s="4" t="s">
-        <v>127</v>
+        <v>124</v>
       </c>
       <c r="K40" s="4"/>
       <c r="L40" s="5" t="s">
-        <v>150</v>
+        <v>147</v>
       </c>
       <c r="M40" s="5"/>
       <c r="N40" s="5"/>
@@ -4767,13 +4729,13 @@
     <row r="41" s="1" customFormat="1" spans="1:15">
       <c r="A41" s="22"/>
       <c r="B41" s="4" t="s">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="C41" s="4"/>
       <c r="D41" s="5"/>
       <c r="E41" s="5"/>
       <c r="F41" s="4" t="s">
-        <v>129</v>
+        <v>126</v>
       </c>
       <c r="G41" s="9"/>
       <c r="H41" s="9"/>
@@ -4802,7 +4764,7 @@
       </c>
       <c r="K42" s="4"/>
       <c r="L42" s="5" t="s">
-        <v>151</v>
+        <v>148</v>
       </c>
       <c r="M42" s="5"/>
       <c r="N42" s="5"/>
@@ -4811,7 +4773,7 @@
     <row r="43" s="1" customFormat="1" spans="1:15">
       <c r="A43" s="22"/>
       <c r="B43" s="23" t="s">
-        <v>130</v>
+        <v>127</v>
       </c>
       <c r="C43" s="23"/>
       <c r="D43" s="23"/>
@@ -4833,18 +4795,18 @@
         <v>29</v>
       </c>
       <c r="C44" s="4" t="s">
-        <v>131</v>
+        <v>128</v>
       </c>
       <c r="D44" s="4"/>
       <c r="E44" s="4" t="s">
-        <v>132</v>
+        <v>129</v>
       </c>
       <c r="F44" s="4" t="s">
-        <v>133</v>
+        <v>130</v>
       </c>
       <c r="G44" s="4"/>
       <c r="H44" s="4" t="s">
-        <v>134</v>
+        <v>131</v>
       </c>
       <c r="I44" s="4"/>
       <c r="J44" s="4"/>
@@ -4860,7 +4822,7 @@
         <v>1</v>
       </c>
       <c r="C45" s="5" t="s">
-        <v>156</v>
+        <v>153</v>
       </c>
       <c r="D45" s="5"/>
       <c r="E45" s="5"/>
